--- a/lorenzo-playwright-kdf/excelFramework/testcases/IP/LSTP_IP_WF001.xlsx
+++ b/lorenzo-playwright-kdf/excelFramework/testcases/IP/LSTP_IP_WF001.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr filterPrivacy="1" updateLinks="always"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{03E166CB-8705-42C0-A9D2-8D79BA31A8B5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5A3FE1AD-190C-4059-8B9C-0C2B5F3429FE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -17,7 +17,7 @@
     <externalReference r:id="rId5"/>
   </externalReferences>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">TestExecution!$A$1:$K$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">TestExecution!$A$1:$L$1</definedName>
     <definedName name="condition">[1]keywordmapping!$P$22:$P$2000</definedName>
     <definedName name="keywordreqcondition">[1]keywordmapping!$R$2:$R$2000</definedName>
     <definedName name="keywordreqproperty">[1]keywordmapping!$Q$2:$Q$2000</definedName>
@@ -1332,7 +1332,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="26">
+  <cellXfs count="25">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
@@ -1366,12 +1366,11 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="3" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
@@ -2733,7 +2732,7 @@
       <c r="J35" s="4"/>
       <c r="K35" s="4"/>
     </row>
-    <row r="36" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:11" ht="15" x14ac:dyDescent="0.25">
       <c r="A36" s="4">
         <v>35</v>
       </c>
@@ -2756,7 +2755,7 @@
       <c r="J36" s="4"/>
       <c r="K36" s="4"/>
     </row>
-    <row r="37" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:11" ht="15" x14ac:dyDescent="0.25">
       <c r="A37" s="4">
         <v>36</v>
       </c>
@@ -3471,7 +3470,7 @@
       <c r="B69" s="11" t="s">
         <v>376</v>
       </c>
-      <c r="C69" s="25" t="s">
+      <c r="C69" s="24" t="s">
         <v>387</v>
       </c>
       <c r="D69" s="12" t="s">
@@ -3488,7 +3487,7 @@
       <c r="B70" s="11" t="s">
         <v>384</v>
       </c>
-      <c r="C70" s="25" t="s">
+      <c r="C70" s="24" t="s">
         <v>389</v>
       </c>
       <c r="D70" s="11" t="s">
@@ -3505,7 +3504,7 @@
       <c r="B71" s="2" t="s">
         <v>317</v>
       </c>
-      <c r="C71" s="25" t="s">
+      <c r="C71" s="24" t="s">
         <v>389</v>
       </c>
       <c r="F71" s="2" t="s">
@@ -3522,7 +3521,7 @@
       <c r="B72" s="11" t="s">
         <v>379</v>
       </c>
-      <c r="C72" s="25" t="s">
+      <c r="C72" s="24" t="s">
         <v>389</v>
       </c>
       <c r="D72" s="12" t="s">
@@ -3558,17 +3557,17 @@
         <v>21</v>
       </c>
     </row>
-    <row r="74" spans="1:11" s="24" customFormat="1" ht="15" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:11" s="21" customFormat="1" ht="15" x14ac:dyDescent="0.25">
       <c r="A74" s="4">
         <v>73</v>
       </c>
-      <c r="B74" s="24" t="s">
+      <c r="B74" s="21" t="s">
         <v>317</v>
       </c>
       <c r="C74" s="23" t="s">
         <v>101</v>
       </c>
-      <c r="F74" s="24" t="s">
+      <c r="F74" s="21" t="s">
         <v>318</v>
       </c>
     </row>
@@ -4983,7 +4982,7 @@
       </c>
     </row>
     <row r="150" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A150" s="24"/>
+      <c r="A150" s="21"/>
     </row>
     <row r="151" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B151" s="16" t="s">
@@ -5023,7 +5022,7 @@
       <c r="C154" s="14"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:K1" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
+  <autoFilter ref="A1:L1" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
   <dataValidations count="5">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F26 F24 F57 F34 F37 F60 F62 F65 F68 F74 F71" xr:uid="{A78A6BD1-DBA3-4AF4-AD65-FEE2CB211C08}">
       <formula1>IF(ISBLANK(#REF!), INDIRECT("keywordnotreqpage"), IF(ISBLANK(#REF!), INDIRECT("keywordnotreqelement"), INDIRECT(LEFT(#REF!,3)&amp;"")))</formula1>
@@ -5461,4 +5460,10 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=docMetadata/LabelInfo.xml><?xml version="1.0" encoding="utf-8"?>
+<clbl:labelList xmlns:clbl="http://schemas.microsoft.com/office/2020/mipLabelMetadata">
+  <clbl:label id="{a4153a30-97aa-49dd-8839-66f72081522c}" enabled="1" method="Standard" siteId="{9ffff5c3-bdfa-4a9d-b595-ff68329945ef}" contentBits="0" removed="0"/>
+</clbl:labelList>
 </file>
--- a/lorenzo-playwright-kdf/excelFramework/testcases/IP/LSTP_IP_WF001.xlsx
+++ b/lorenzo-playwright-kdf/excelFramework/testcases/IP/LSTP_IP_WF001.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr filterPrivacy="1" updateLinks="always"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{03E166CB-8705-42C0-A9D2-8D79BA31A8B5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FE66FBF3-1756-48D7-8E8D-2154E52AF80C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28,11 +28,12 @@
     <definedName name="tablecondition">[1]keywordmapping!$U$2:$U$2000</definedName>
   </definedNames>
   <calcPr calcId="171027"/>
+  <fileRecoveryPr repairLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="765" uniqueCount="393">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="759" uniqueCount="387">
   <si>
     <t>StepNo</t>
   </si>
@@ -202,9 +203,6 @@
     <t>txt_Forename</t>
   </si>
   <si>
-    <t>Alexa</t>
-  </si>
-  <si>
     <t>txt_DOB</t>
   </si>
   <si>
@@ -379,9 +377,6 @@
     <t>Click Finish now to save updated booking details</t>
   </si>
   <si>
-    <t>Validate updated booking details are saved correctly</t>
-  </si>
-  <si>
     <t>txt_Admissiondate</t>
   </si>
   <si>
@@ -391,15 +386,9 @@
     <t>Click Admit to initiate patient admission</t>
   </si>
   <si>
-    <t>Admit</t>
-  </si>
-  <si>
     <t>Select admission source</t>
   </si>
   <si>
-    <t>pagePatADMAdmission</t>
-  </si>
-  <si>
     <t>cmb_AdmissionSource</t>
   </si>
   <si>
@@ -418,39 +407,21 @@
     <t>Select intended management for admission</t>
   </si>
   <si>
-    <t>cmb_intended management</t>
-  </si>
-  <si>
     <t>Click Next to proceed to admission road map</t>
   </si>
   <si>
-    <t>Select Care Provider via SFS</t>
-  </si>
-  <si>
     <t>pageAdmitIPAdmitRoad</t>
   </si>
   <si>
     <t>ico_CareProviderSFS</t>
   </si>
   <si>
-    <t>Enter care provider identifier</t>
-  </si>
-  <si>
-    <t>pageAdmitIPAdmitRoadCPSFS</t>
-  </si>
-  <si>
     <t>txt_Identifier</t>
   </si>
   <si>
     <t>CARE_PROVIDER_ID</t>
   </si>
   <si>
-    <t>Click Find to search for care provider</t>
-  </si>
-  <si>
-    <t>Click Ok to select care provider</t>
-  </si>
-  <si>
     <t>btn_Ok</t>
   </si>
   <si>
@@ -466,9 +437,6 @@
     <t>cmb_BedCategory</t>
   </si>
   <si>
-    <t>Index_0</t>
-  </si>
-  <si>
     <t>Click Finish now to complete admission</t>
   </si>
   <si>
@@ -1093,9 +1061,6 @@
     <t>Click Finish in manage referral</t>
   </si>
   <si>
-    <t>996289289500</t>
-  </si>
-  <si>
     <t>Click on Finish now</t>
   </si>
   <si>
@@ -1165,33 +1130,15 @@
     <t>Click on Inpatient History</t>
   </si>
   <si>
-    <t>//td[img[@alt='Click to select row']]</t>
-  </si>
-  <si>
-    <t>//td[@ival='Booked']</t>
-  </si>
-  <si>
-    <t>Verify the Status Booked</t>
-  </si>
-  <si>
     <t>tbl_IPHistorySelectRow</t>
   </si>
   <si>
-    <t>tbl_IPHistoryVerifystatus</t>
-  </si>
-  <si>
     <t>tbl_IPHistoryCurrentview</t>
   </si>
   <si>
-    <t>//td[@caption='Current View']</t>
-  </si>
-  <si>
     <t>Select the Booked Appointment details</t>
   </si>
   <si>
-    <t>Booked</t>
-  </si>
-  <si>
     <t>Navigate back to Current view</t>
   </si>
   <si>
@@ -1204,20 +1151,56 @@
     <t>pagePbrdHistory</t>
   </si>
   <si>
-    <t>verifyproperty</t>
-  </si>
-  <si>
-    <t>value</t>
-  </si>
-  <si>
-    <t>Contains</t>
+    <t>Click on Edit Booked patient</t>
+  </si>
+  <si>
+    <t>Scheduled sequence of at least one overnight admissions</t>
+  </si>
+  <si>
+    <t>0|Cancel</t>
+  </si>
+  <si>
+    <t>Overseas popup Information message cancel</t>
+  </si>
+  <si>
+    <t>Elective Admission: Planned</t>
+  </si>
+  <si>
+    <t>Scheduled sequence of night admissions</t>
+  </si>
+  <si>
+    <t>Critical care</t>
+  </si>
+  <si>
+    <t>wait for Roller</t>
+  </si>
+  <si>
+    <t>wait for Roller in home</t>
+  </si>
+  <si>
+    <t>lnk_AdmitTaskPane</t>
+  </si>
+  <si>
+    <t>forename||_Randomforename</t>
+  </si>
+  <si>
+    <t>_Randomforename</t>
+  </si>
+  <si>
+    <t>Generate random forename for new patient</t>
+  </si>
+  <si>
+    <t>Temporary place of residence</t>
+  </si>
+  <si>
+    <t>cmb_intendedManagement</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="6" x14ac:knownFonts="1">
+  <fonts count="9" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1261,6 +1244,25 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF242424"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="15"/>
+      <name val="Consolas"/>
+      <family val="3"/>
+    </font>
   </fonts>
   <fills count="6">
     <fill>
@@ -1294,7 +1296,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="3">
+  <borders count="4">
     <border>
       <left/>
       <right/>
@@ -1318,9 +1320,7 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
+      <left/>
       <right style="thin">
         <color indexed="64"/>
       </right>
@@ -1328,11 +1328,24 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="26">
+  <cellXfs count="34">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
@@ -1342,37 +1355,49 @@
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
-    <xf numFmtId="49" fontId="0" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="14" fontId="0" fillId="3" borderId="1" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="0" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="1" fontId="7" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1863,24 +1888,25 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:L154"/>
+  <dimension ref="A1:L159"/>
   <sheetFormatPr defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="48.42578125" customWidth="1"/>
-    <col min="3" max="3" width="31.7109375" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="25.5703125" customWidth="1"/>
-    <col min="5" max="5" width="21.140625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="22.42578125" customWidth="1"/>
-    <col min="7" max="7" width="13.28515625" customWidth="1"/>
-    <col min="8" max="8" width="16.140625" customWidth="1"/>
-    <col min="9" max="9" width="19.5703125" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="47.140625" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="27.140625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="9.140625" style="22"/>
+    <col min="2" max="2" width="48.42578125" style="6" customWidth="1"/>
+    <col min="3" max="3" width="31.7109375" style="6" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="25.5703125" style="6" customWidth="1"/>
+    <col min="5" max="5" width="21.140625" style="6" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="22.42578125" style="6" customWidth="1"/>
+    <col min="7" max="7" width="13.28515625" style="6" customWidth="1"/>
+    <col min="8" max="8" width="16.140625" style="6" customWidth="1"/>
+    <col min="9" max="9" width="19.5703125" style="6" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="47.140625" style="6" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="27.140625" style="6" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="14" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:12" ht="15" x14ac:dyDescent="0.25">
-      <c r="A1" s="5" t="s">
+      <c r="A1" s="27" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="5" t="s">
@@ -1913,12 +1939,12 @@
       <c r="K1" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="20" t="s">
-        <v>388</v>
-      </c>
-    </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A2" s="4">
+      <c r="L1" s="16" t="s">
+        <v>370</v>
+      </c>
+    </row>
+    <row r="2" spans="1:12" ht="15" x14ac:dyDescent="0.25">
+      <c r="A2" s="22">
         <v>1</v>
       </c>
       <c r="B2" s="4" t="s">
@@ -1937,13 +1963,13 @@
       <c r="G2" s="4"/>
       <c r="H2" s="4"/>
       <c r="I2" s="4"/>
-      <c r="J2" s="4">
-        <v>996289289500</v>
+      <c r="J2" s="32">
+        <v>996289289033</v>
       </c>
       <c r="K2" s="4"/>
     </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A3" s="4">
+    <row r="3" spans="1:12" ht="15" x14ac:dyDescent="0.25">
+      <c r="A3" s="22">
         <v>2</v>
       </c>
       <c r="B3" s="4" t="s">
@@ -1967,8 +1993,8 @@
       </c>
       <c r="K3" s="4"/>
     </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A4" s="4">
+    <row r="4" spans="1:12" ht="15" x14ac:dyDescent="0.25">
+      <c r="A4" s="22">
         <v>3</v>
       </c>
       <c r="B4" s="4" t="s">
@@ -1990,8 +2016,8 @@
       <c r="J4" s="4"/>
       <c r="K4" s="4"/>
     </row>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A5" s="4">
+    <row r="5" spans="1:12" ht="15" x14ac:dyDescent="0.25">
+      <c r="A5" s="22">
         <v>4</v>
       </c>
       <c r="B5" s="4" t="s">
@@ -2013,8 +2039,8 @@
       <c r="J5" s="4"/>
       <c r="K5" s="4"/>
     </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A6" s="4">
+    <row r="6" spans="1:12" ht="15" x14ac:dyDescent="0.25">
+      <c r="A6" s="22">
         <v>5</v>
       </c>
       <c r="B6" s="4" t="s">
@@ -2038,8 +2064,8 @@
       <c r="J6" s="4"/>
       <c r="K6" s="4"/>
     </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A7" s="4">
+    <row r="7" spans="1:12" ht="15" x14ac:dyDescent="0.25">
+      <c r="A7" s="22">
         <v>6</v>
       </c>
       <c r="B7" s="4" t="s">
@@ -2061,8 +2087,8 @@
       <c r="J7" s="4"/>
       <c r="K7" s="4"/>
     </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A8" s="4">
+    <row r="8" spans="1:12" ht="15" x14ac:dyDescent="0.25">
+      <c r="A8" s="22">
         <v>7</v>
       </c>
       <c r="B8" s="4" t="s">
@@ -2086,8 +2112,8 @@
       <c r="J8" s="4"/>
       <c r="K8" s="4"/>
     </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A9" s="4">
+    <row r="9" spans="1:12" ht="15" x14ac:dyDescent="0.25">
+      <c r="A9" s="22">
         <v>8</v>
       </c>
       <c r="B9" s="4" t="s">
@@ -2109,8 +2135,8 @@
       <c r="J9" s="4"/>
       <c r="K9" s="4"/>
     </row>
-    <row r="10" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A10" s="4">
+    <row r="10" spans="1:12" ht="15" x14ac:dyDescent="0.25">
+      <c r="A10" s="22">
         <v>9</v>
       </c>
       <c r="B10" s="4" t="s">
@@ -2132,8 +2158,8 @@
       <c r="J10" s="4"/>
       <c r="K10" s="4"/>
     </row>
-    <row r="11" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A11" s="4">
+    <row r="11" spans="1:12" ht="15" x14ac:dyDescent="0.25">
+      <c r="A11" s="22">
         <v>10</v>
       </c>
       <c r="B11" s="4" t="s">
@@ -2157,8 +2183,8 @@
       <c r="J11" s="4"/>
       <c r="K11" s="4"/>
     </row>
-    <row r="12" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A12" s="4">
+    <row r="12" spans="1:12" ht="15" x14ac:dyDescent="0.25">
+      <c r="A12" s="22">
         <v>11</v>
       </c>
       <c r="B12" s="4" t="s">
@@ -2192,8 +2218,8 @@
         <v>43</v>
       </c>
     </row>
-    <row r="13" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A13" s="4">
+    <row r="13" spans="1:12" ht="15" x14ac:dyDescent="0.25">
+      <c r="A13" s="22">
         <v>12</v>
       </c>
       <c r="B13" s="4" t="s">
@@ -2215,164 +2241,164 @@
       </c>
       <c r="K13" s="4"/>
     </row>
-    <row r="14" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A14" s="4">
+    <row r="14" spans="1:12" ht="15" x14ac:dyDescent="0.25">
+      <c r="A14" s="22">
         <v>13</v>
       </c>
       <c r="B14" s="4" t="s">
-        <v>48</v>
+        <v>384</v>
       </c>
       <c r="C14" s="4" t="s">
         <v>42</v>
       </c>
-      <c r="D14" s="4" t="s">
-        <v>49</v>
-      </c>
+      <c r="D14" s="4"/>
       <c r="E14" s="4"/>
-      <c r="F14" s="4" t="s">
+      <c r="F14" s="30" t="s">
+        <v>46</v>
+      </c>
+      <c r="G14" s="30"/>
+      <c r="H14" s="30"/>
+      <c r="I14" s="30"/>
+      <c r="J14" s="30" t="s">
+        <v>382</v>
+      </c>
+      <c r="K14" s="4"/>
+    </row>
+    <row r="15" spans="1:12" ht="15" x14ac:dyDescent="0.25">
+      <c r="A15" s="22">
         <v>14</v>
       </c>
-      <c r="G14" s="4"/>
-      <c r="H14" s="4"/>
-      <c r="I14" s="4"/>
-      <c r="J14" s="4" t="s">
-        <v>50</v>
-      </c>
-      <c r="K14" s="4"/>
-    </row>
-    <row r="15" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A15" s="4">
-        <v>14</v>
-      </c>
       <c r="B15" s="4" t="s">
-        <v>323</v>
+        <v>48</v>
       </c>
       <c r="C15" s="4" t="s">
         <v>42</v>
       </c>
       <c r="D15" s="4" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="E15" s="4"/>
       <c r="F15" s="4" t="s">
-        <v>52</v>
+        <v>14</v>
       </c>
       <c r="G15" s="4"/>
       <c r="H15" s="4"/>
       <c r="I15" s="4"/>
       <c r="J15" s="4" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="K15" s="4"/>
     </row>
-    <row r="16" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A16" s="4">
+    <row r="16" spans="1:12" ht="15" x14ac:dyDescent="0.25">
+      <c r="A16" s="22">
         <v>15</v>
       </c>
       <c r="B16" s="4" t="s">
-        <v>54</v>
+        <v>312</v>
       </c>
       <c r="C16" s="4" t="s">
         <v>42</v>
       </c>
       <c r="D16" s="4" t="s">
-        <v>55</v>
+        <v>51</v>
       </c>
       <c r="E16" s="4"/>
       <c r="F16" s="4" t="s">
-        <v>14</v>
+        <v>52</v>
       </c>
       <c r="G16" s="4"/>
       <c r="H16" s="4"/>
       <c r="I16" s="4"/>
       <c r="J16" s="4" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="K16" s="4"/>
     </row>
-    <row r="17" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A17" s="4">
+    <row r="17" spans="1:12" ht="15" x14ac:dyDescent="0.25">
+      <c r="A17" s="22">
         <v>16</v>
       </c>
       <c r="B17" s="4" t="s">
-        <v>325</v>
+        <v>54</v>
       </c>
       <c r="C17" s="4" t="s">
         <v>42</v>
       </c>
       <c r="D17" s="4" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="E17" s="4"/>
       <c r="F17" s="4" t="s">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="G17" s="4"/>
       <c r="H17" s="4"/>
       <c r="I17" s="4"/>
-      <c r="J17" s="4"/>
+      <c r="J17" s="4" t="s">
+        <v>383</v>
+      </c>
       <c r="K17" s="4"/>
     </row>
-    <row r="18" spans="1:11" ht="15" x14ac:dyDescent="0.25">
-      <c r="A18" s="4">
+    <row r="18" spans="1:12" ht="15" x14ac:dyDescent="0.25">
+      <c r="A18" s="22">
         <v>17</v>
       </c>
       <c r="B18" s="4" t="s">
-        <v>324</v>
+        <v>314</v>
       </c>
       <c r="C18" s="4" t="s">
         <v>42</v>
       </c>
       <c r="D18" s="4" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="E18" s="4"/>
       <c r="F18" s="4" t="s">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="G18" s="4"/>
       <c r="H18" s="4"/>
       <c r="I18" s="4"/>
-      <c r="J18" s="8" t="s">
-        <v>363</v>
-      </c>
+      <c r="J18" s="4"/>
       <c r="K18" s="4"/>
     </row>
-    <row r="19" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A19" s="4">
+    <row r="19" spans="1:12" ht="15" x14ac:dyDescent="0.25">
+      <c r="A19" s="22">
         <v>18</v>
       </c>
       <c r="B19" s="4" t="s">
-        <v>58</v>
+        <v>313</v>
       </c>
       <c r="C19" s="4" t="s">
         <v>42</v>
       </c>
       <c r="D19" s="4" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="E19" s="4"/>
       <c r="F19" s="4" t="s">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="G19" s="4"/>
       <c r="H19" s="4"/>
       <c r="I19" s="4"/>
-      <c r="J19" s="4"/>
+      <c r="J19" s="7" t="s">
+        <v>351</v>
+      </c>
       <c r="K19" s="4"/>
     </row>
-    <row r="20" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A20" s="4">
+    <row r="20" spans="1:12" ht="15" x14ac:dyDescent="0.25">
+      <c r="A20" s="22">
         <v>19</v>
       </c>
       <c r="B20" s="4" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="C20" s="4" t="s">
-        <v>61</v>
+        <v>42</v>
       </c>
       <c r="D20" s="4" t="s">
-        <v>62</v>
+        <v>58</v>
       </c>
       <c r="E20" s="4"/>
       <c r="F20" s="4" t="s">
@@ -2384,367 +2410,369 @@
       <c r="J20" s="4"/>
       <c r="K20" s="4"/>
     </row>
-    <row r="21" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A21" s="4">
+    <row r="21" spans="1:12" ht="15" x14ac:dyDescent="0.25">
+      <c r="A21" s="22">
         <v>20</v>
       </c>
       <c r="B21" s="4" t="s">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="C21" s="4" t="s">
+        <v>60</v>
+      </c>
+      <c r="D21" s="4" t="s">
         <v>61</v>
-      </c>
-      <c r="D21" s="4" t="s">
-        <v>64</v>
       </c>
       <c r="E21" s="4"/>
       <c r="F21" s="4" t="s">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="G21" s="4"/>
       <c r="H21" s="4"/>
       <c r="I21" s="4"/>
       <c r="J21" s="4"/>
-      <c r="K21" s="4" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="22" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A22" s="4">
+      <c r="K21" s="4"/>
+    </row>
+    <row r="22" spans="1:12" ht="15" x14ac:dyDescent="0.25">
+      <c r="A22" s="22">
         <v>21</v>
       </c>
       <c r="B22" s="4" t="s">
-        <v>66</v>
+        <v>62</v>
       </c>
       <c r="C22" s="4" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="D22" s="4" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="E22" s="4"/>
       <c r="F22" s="4" t="s">
-        <v>52</v>
+        <v>14</v>
       </c>
       <c r="G22" s="4"/>
       <c r="H22" s="4"/>
       <c r="I22" s="4"/>
       <c r="J22" s="4"/>
       <c r="K22" s="4" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="23" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A23" s="4">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="23" spans="1:12" ht="15" x14ac:dyDescent="0.25">
+      <c r="A23" s="22">
         <v>22</v>
       </c>
       <c r="B23" s="4" t="s">
-        <v>69</v>
-      </c>
-      <c r="C23" s="6" t="s">
-        <v>61</v>
-      </c>
-      <c r="D23" s="6" t="s">
-        <v>355</v>
+        <v>65</v>
+      </c>
+      <c r="C23" s="4" t="s">
+        <v>60</v>
+      </c>
+      <c r="D23" s="4" t="s">
+        <v>66</v>
       </c>
       <c r="E23" s="4"/>
       <c r="F23" s="4" t="s">
-        <v>21</v>
+        <v>52</v>
       </c>
       <c r="G23" s="4"/>
       <c r="H23" s="4"/>
       <c r="I23" s="4"/>
       <c r="J23" s="4"/>
-      <c r="K23" s="4"/>
-    </row>
-    <row r="24" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A24" s="4">
+      <c r="K23" s="4" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="24" spans="1:12" ht="15" x14ac:dyDescent="0.25">
+      <c r="A24" s="22">
         <v>23</v>
       </c>
       <c r="B24" s="4" t="s">
-        <v>317</v>
-      </c>
-      <c r="C24" s="4" t="s">
-        <v>70</v>
-      </c>
-      <c r="D24" s="4"/>
+        <v>68</v>
+      </c>
+      <c r="C24" s="6" t="s">
+        <v>60</v>
+      </c>
+      <c r="D24" s="6" t="s">
+        <v>343</v>
+      </c>
       <c r="E24" s="4"/>
       <c r="F24" s="4" t="s">
-        <v>318</v>
+        <v>21</v>
       </c>
       <c r="G24" s="4"/>
       <c r="H24" s="4"/>
       <c r="I24" s="4"/>
-      <c r="J24" s="4">
-        <v>7</v>
-      </c>
+      <c r="J24" s="4"/>
       <c r="K24" s="4"/>
     </row>
-    <row r="25" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A25" s="4">
+    <row r="25" spans="1:12" ht="15" x14ac:dyDescent="0.25">
+      <c r="A25" s="22">
         <v>24</v>
       </c>
       <c r="B25" s="4" t="s">
-        <v>322</v>
+        <v>306</v>
       </c>
       <c r="C25" s="4" t="s">
-        <v>70</v>
-      </c>
-      <c r="D25" s="6" t="s">
-        <v>356</v>
-      </c>
+        <v>69</v>
+      </c>
+      <c r="D25" s="4"/>
       <c r="E25" s="4"/>
       <c r="F25" s="4" t="s">
-        <v>21</v>
+        <v>307</v>
       </c>
       <c r="G25" s="4"/>
       <c r="H25" s="4"/>
       <c r="I25" s="4"/>
-      <c r="J25" s="4"/>
+      <c r="J25" s="4">
+        <v>7</v>
+      </c>
       <c r="K25" s="4"/>
     </row>
-    <row r="26" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A26" s="4">
+    <row r="26" spans="1:12" ht="15" x14ac:dyDescent="0.25">
+      <c r="A26" s="22">
         <v>25</v>
       </c>
       <c r="B26" s="4" t="s">
-        <v>317</v>
+        <v>311</v>
       </c>
       <c r="C26" s="4" t="s">
-        <v>70</v>
-      </c>
-      <c r="D26" s="4"/>
+        <v>69</v>
+      </c>
+      <c r="D26" s="6" t="s">
+        <v>344</v>
+      </c>
       <c r="E26" s="4"/>
       <c r="F26" s="4" t="s">
-        <v>318</v>
+        <v>21</v>
       </c>
       <c r="G26" s="4"/>
       <c r="H26" s="4"/>
       <c r="I26" s="4"/>
-      <c r="J26" s="4">
-        <v>7</v>
-      </c>
+      <c r="J26" s="4"/>
       <c r="K26" s="4"/>
     </row>
-    <row r="27" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A27" s="4">
+    <row r="27" spans="1:12" ht="15" x14ac:dyDescent="0.25">
+      <c r="A27" s="22">
         <v>26</v>
       </c>
       <c r="B27" s="4" t="s">
-        <v>319</v>
+        <v>306</v>
       </c>
       <c r="C27" s="4" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="D27" s="4"/>
       <c r="E27" s="4"/>
       <c r="F27" s="4" t="s">
-        <v>315</v>
+        <v>307</v>
       </c>
       <c r="G27" s="4"/>
       <c r="H27" s="4"/>
       <c r="I27" s="4"/>
-      <c r="J27" s="4" t="s">
-        <v>316</v>
+      <c r="J27" s="4">
+        <v>7</v>
       </c>
       <c r="K27" s="4"/>
     </row>
-    <row r="28" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="4">
+    <row r="28" spans="1:12" ht="15" x14ac:dyDescent="0.25">
+      <c r="A28" s="22">
         <v>27</v>
       </c>
       <c r="B28" s="4" t="s">
-        <v>320</v>
+        <v>308</v>
       </c>
       <c r="C28" s="4" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="D28" s="4"/>
       <c r="E28" s="4"/>
       <c r="F28" s="4" t="s">
-        <v>315</v>
+        <v>304</v>
       </c>
       <c r="G28" s="4"/>
       <c r="H28" s="4"/>
       <c r="I28" s="4"/>
       <c r="J28" s="4" t="s">
-        <v>321</v>
+        <v>305</v>
       </c>
       <c r="K28" s="4"/>
     </row>
-    <row r="29" spans="1:11" s="4" customFormat="1" ht="15" x14ac:dyDescent="0.25">
-      <c r="A29" s="4">
+    <row r="29" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A29" s="22">
         <v>28</v>
       </c>
       <c r="B29" s="4" t="s">
-        <v>362</v>
+        <v>309</v>
       </c>
       <c r="C29" s="4" t="s">
+        <v>69</v>
+      </c>
+      <c r="D29" s="4"/>
+      <c r="E29" s="4"/>
+      <c r="F29" s="4" t="s">
+        <v>304</v>
+      </c>
+      <c r="G29" s="4"/>
+      <c r="H29" s="4"/>
+      <c r="I29" s="4"/>
+      <c r="J29" s="4" t="s">
+        <v>310</v>
+      </c>
+      <c r="K29" s="4"/>
+    </row>
+    <row r="30" spans="1:12" s="4" customFormat="1" ht="15" x14ac:dyDescent="0.25">
+      <c r="A30" s="22">
+        <v>29</v>
+      </c>
+      <c r="B30" s="4" t="s">
+        <v>350</v>
+      </c>
+      <c r="C30" s="4" t="s">
+        <v>69</v>
+      </c>
+      <c r="D30" s="4" t="s">
+        <v>349</v>
+      </c>
+      <c r="F30" s="6" t="s">
+        <v>115</v>
+      </c>
+      <c r="J30" s="6" t="s">
+        <v>353</v>
+      </c>
+      <c r="L30" s="17"/>
+    </row>
+    <row r="31" spans="1:12" s="8" customFormat="1" ht="15" x14ac:dyDescent="0.25">
+      <c r="A31" s="22">
+        <v>30</v>
+      </c>
+      <c r="B31" s="19" t="s">
+        <v>354</v>
+      </c>
+      <c r="C31" s="8" t="s">
+        <v>69</v>
+      </c>
+      <c r="D31" s="19"/>
+      <c r="E31" s="19"/>
+      <c r="F31" s="19" t="s">
+        <v>355</v>
+      </c>
+      <c r="G31" s="19"/>
+      <c r="H31" s="19"/>
+      <c r="I31" s="19"/>
+      <c r="J31" s="19" t="s">
+        <v>356</v>
+      </c>
+      <c r="L31" s="18"/>
+    </row>
+    <row r="32" spans="1:12" ht="15" x14ac:dyDescent="0.25">
+      <c r="A32" s="22">
+        <v>31</v>
+      </c>
+      <c r="B32" s="4" t="s">
         <v>70</v>
       </c>
-      <c r="D29" s="4" t="s">
-        <v>361</v>
-      </c>
-      <c r="F29" t="s">
-        <v>117</v>
-      </c>
-      <c r="J29" t="s">
-        <v>365</v>
-      </c>
-    </row>
-    <row r="30" spans="1:11" s="9" customFormat="1" ht="15" x14ac:dyDescent="0.25">
-      <c r="A30" s="4">
-        <v>29</v>
-      </c>
-      <c r="B30" s="10" t="s">
-        <v>366</v>
-      </c>
-      <c r="C30" s="9" t="s">
-        <v>70</v>
-      </c>
-      <c r="D30" s="10"/>
-      <c r="E30" s="10"/>
-      <c r="F30" s="10" t="s">
-        <v>367</v>
-      </c>
-      <c r="G30" s="10"/>
-      <c r="H30" s="10"/>
-      <c r="I30" s="10"/>
-      <c r="J30" s="10" t="s">
-        <v>368</v>
-      </c>
-    </row>
-    <row r="31" spans="1:11" ht="15" x14ac:dyDescent="0.25">
-      <c r="A31" s="4">
-        <v>30</v>
-      </c>
-      <c r="B31" s="4" t="s">
+      <c r="C32" s="4" t="s">
         <v>71</v>
       </c>
-      <c r="C31" s="4" t="s">
+      <c r="D32" s="4" t="s">
         <v>72</v>
-      </c>
-      <c r="D31" s="4" t="s">
-        <v>73</v>
-      </c>
-      <c r="E31" s="4"/>
-      <c r="F31" s="4" t="s">
-        <v>52</v>
-      </c>
-      <c r="G31" s="4"/>
-      <c r="H31" s="4"/>
-      <c r="I31" s="4"/>
-      <c r="J31" s="4"/>
-      <c r="K31" s="4" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="32" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A32" s="4">
-        <v>31</v>
-      </c>
-      <c r="B32" s="4" t="s">
-        <v>326</v>
-      </c>
-      <c r="C32" s="4" t="s">
-        <v>72</v>
-      </c>
-      <c r="D32" s="4" t="s">
-        <v>327</v>
       </c>
       <c r="E32" s="4"/>
       <c r="F32" s="4" t="s">
-        <v>14</v>
+        <v>52</v>
       </c>
       <c r="G32" s="4"/>
       <c r="H32" s="4"/>
       <c r="I32" s="4"/>
       <c r="J32" s="4"/>
       <c r="K32" s="4" t="s">
-        <v>328</v>
-      </c>
-    </row>
-    <row r="33" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A33" s="4">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="33" spans="1:11" ht="15" x14ac:dyDescent="0.25">
+      <c r="A33" s="22">
         <v>32</v>
       </c>
       <c r="B33" s="4" t="s">
-        <v>75</v>
+        <v>315</v>
       </c>
       <c r="C33" s="4" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="D33" s="4" t="s">
-        <v>76</v>
+        <v>316</v>
       </c>
       <c r="E33" s="4"/>
       <c r="F33" s="4" t="s">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="G33" s="4"/>
       <c r="H33" s="4"/>
       <c r="I33" s="4"/>
       <c r="J33" s="4"/>
-      <c r="K33" s="4"/>
-    </row>
-    <row r="34" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A34" s="4">
+      <c r="K33" s="4" t="s">
+        <v>317</v>
+      </c>
+    </row>
+    <row r="34" spans="1:11" ht="15" x14ac:dyDescent="0.25">
+      <c r="A34" s="22">
         <v>33</v>
       </c>
       <c r="B34" s="4" t="s">
-        <v>317</v>
+        <v>74</v>
       </c>
       <c r="C34" s="4" t="s">
-        <v>72</v>
-      </c>
-      <c r="D34" s="4"/>
+        <v>71</v>
+      </c>
+      <c r="D34" s="4" t="s">
+        <v>75</v>
+      </c>
       <c r="E34" s="4"/>
       <c r="F34" s="4" t="s">
-        <v>318</v>
+        <v>21</v>
       </c>
       <c r="G34" s="4"/>
       <c r="H34" s="4"/>
       <c r="I34" s="4"/>
-      <c r="J34" s="4">
-        <v>10</v>
-      </c>
+      <c r="J34" s="4"/>
       <c r="K34" s="4"/>
     </row>
-    <row r="35" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A35" s="4">
+    <row r="35" spans="1:11" ht="15" x14ac:dyDescent="0.25">
+      <c r="A35" s="22">
         <v>34</v>
       </c>
       <c r="B35" s="4" t="s">
-        <v>77</v>
+        <v>306</v>
       </c>
       <c r="C35" s="4" t="s">
-        <v>72</v>
-      </c>
-      <c r="D35" s="4" t="s">
-        <v>78</v>
-      </c>
+        <v>71</v>
+      </c>
+      <c r="D35" s="4"/>
       <c r="E35" s="4"/>
       <c r="F35" s="4" t="s">
-        <v>21</v>
+        <v>307</v>
       </c>
       <c r="G35" s="4"/>
       <c r="H35" s="4"/>
       <c r="I35" s="4"/>
-      <c r="J35" s="4"/>
+      <c r="J35" s="4">
+        <v>10</v>
+      </c>
       <c r="K35" s="4"/>
     </row>
-    <row r="36" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A36" s="4">
+    <row r="36" spans="1:11" ht="15" x14ac:dyDescent="0.25">
+      <c r="A36" s="22">
         <v>35</v>
       </c>
       <c r="B36" s="4" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="C36" s="4" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="D36" s="4" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="E36" s="4"/>
       <c r="F36" s="4" t="s">
@@ -2756,112 +2784,112 @@
       <c r="J36" s="4"/>
       <c r="K36" s="4"/>
     </row>
-    <row r="37" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A37" s="4">
+    <row r="37" spans="1:11" ht="15" x14ac:dyDescent="0.25">
+      <c r="A37" s="22">
         <v>36</v>
       </c>
       <c r="B37" s="4" t="s">
-        <v>317</v>
+        <v>78</v>
       </c>
       <c r="C37" s="4" t="s">
-        <v>82</v>
-      </c>
-      <c r="D37" s="4"/>
+        <v>71</v>
+      </c>
+      <c r="D37" s="4" t="s">
+        <v>79</v>
+      </c>
       <c r="E37" s="4"/>
       <c r="F37" s="4" t="s">
-        <v>318</v>
+        <v>21</v>
       </c>
       <c r="G37" s="4"/>
       <c r="H37" s="4"/>
       <c r="I37" s="4"/>
-      <c r="J37" s="4">
-        <v>10</v>
-      </c>
+      <c r="J37" s="4"/>
       <c r="K37" s="4"/>
     </row>
     <row r="38" spans="1:11" ht="15" x14ac:dyDescent="0.25">
-      <c r="A38" s="4">
+      <c r="A38" s="22">
         <v>37</v>
       </c>
       <c r="B38" s="4" t="s">
-        <v>330</v>
+        <v>306</v>
       </c>
       <c r="C38" s="4" t="s">
-        <v>82</v>
-      </c>
-      <c r="D38" s="4" t="s">
-        <v>132</v>
-      </c>
+        <v>81</v>
+      </c>
+      <c r="D38" s="4"/>
       <c r="E38" s="4"/>
       <c r="F38" s="4" t="s">
-        <v>21</v>
+        <v>307</v>
       </c>
       <c r="G38" s="4"/>
       <c r="H38" s="4"/>
       <c r="I38" s="4"/>
-      <c r="J38" s="4"/>
+      <c r="J38" s="4">
+        <v>10</v>
+      </c>
       <c r="K38" s="4"/>
     </row>
     <row r="39" spans="1:11" ht="15" x14ac:dyDescent="0.25">
-      <c r="A39" s="4">
+      <c r="A39" s="22">
         <v>38</v>
       </c>
       <c r="B39" s="4" t="s">
-        <v>331</v>
+        <v>319</v>
       </c>
       <c r="C39" s="4" t="s">
-        <v>334</v>
+        <v>81</v>
       </c>
       <c r="D39" s="4" t="s">
-        <v>135</v>
+        <v>126</v>
       </c>
       <c r="E39" s="4"/>
       <c r="F39" s="4" t="s">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="G39" s="4"/>
       <c r="H39" s="4"/>
       <c r="I39" s="4"/>
-      <c r="J39" s="4">
-        <v>996289289500</v>
-      </c>
+      <c r="J39" s="4"/>
       <c r="K39" s="4"/>
     </row>
     <row r="40" spans="1:11" ht="15" x14ac:dyDescent="0.25">
-      <c r="A40" s="4">
+      <c r="A40" s="22">
         <v>39</v>
       </c>
       <c r="B40" s="4" t="s">
-        <v>332</v>
+        <v>320</v>
       </c>
       <c r="C40" s="4" t="s">
-        <v>334</v>
+        <v>323</v>
       </c>
       <c r="D40" s="4" t="s">
-        <v>59</v>
+        <v>127</v>
       </c>
       <c r="E40" s="4"/>
       <c r="F40" s="4" t="s">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="G40" s="4"/>
       <c r="H40" s="4"/>
       <c r="I40" s="4"/>
-      <c r="J40" s="4"/>
+      <c r="J40" s="33">
+        <v>996289289033</v>
+      </c>
       <c r="K40" s="4"/>
     </row>
     <row r="41" spans="1:11" ht="15" x14ac:dyDescent="0.25">
-      <c r="A41" s="4">
+      <c r="A41" s="22">
         <v>40</v>
       </c>
       <c r="B41" s="4" t="s">
-        <v>333</v>
+        <v>321</v>
       </c>
       <c r="C41" s="4" t="s">
-        <v>334</v>
+        <v>323</v>
       </c>
       <c r="D41" s="4" t="s">
-        <v>139</v>
+        <v>58</v>
       </c>
       <c r="E41" s="4"/>
       <c r="F41" s="4" t="s">
@@ -2874,90 +2902,88 @@
       <c r="K41" s="4"/>
     </row>
     <row r="42" spans="1:11" ht="15" x14ac:dyDescent="0.25">
-      <c r="A42" s="4">
+      <c r="A42" s="22">
         <v>41</v>
       </c>
       <c r="B42" s="4" t="s">
-        <v>81</v>
+        <v>322</v>
       </c>
       <c r="C42" s="4" t="s">
-        <v>82</v>
+        <v>323</v>
       </c>
       <c r="D42" s="4" t="s">
-        <v>83</v>
+        <v>129</v>
       </c>
       <c r="E42" s="4"/>
       <c r="F42" s="4" t="s">
-        <v>52</v>
+        <v>21</v>
       </c>
       <c r="G42" s="4"/>
       <c r="H42" s="4"/>
       <c r="I42" s="4"/>
       <c r="J42" s="4"/>
-      <c r="K42" s="4" t="s">
-        <v>84</v>
-      </c>
+      <c r="K42" s="4"/>
     </row>
     <row r="43" spans="1:11" ht="15" x14ac:dyDescent="0.25">
-      <c r="A43" s="4">
+      <c r="A43" s="22">
         <v>42</v>
       </c>
       <c r="B43" s="4" t="s">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="C43" s="4" t="s">
+        <v>81</v>
+      </c>
+      <c r="D43" s="4" t="s">
         <v>82</v>
-      </c>
-      <c r="D43" s="4" t="s">
-        <v>86</v>
       </c>
       <c r="E43" s="4"/>
       <c r="F43" s="4" t="s">
-        <v>21</v>
+        <v>52</v>
       </c>
       <c r="G43" s="4"/>
       <c r="H43" s="4"/>
       <c r="I43" s="4"/>
       <c r="J43" s="4"/>
-      <c r="K43" s="4"/>
+      <c r="K43" s="4" t="s">
+        <v>83</v>
+      </c>
     </row>
     <row r="44" spans="1:11" ht="15" x14ac:dyDescent="0.25">
-      <c r="A44" s="4">
+      <c r="A44" s="22">
         <v>43</v>
       </c>
       <c r="B44" s="4" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="C44" s="4" t="s">
-        <v>88</v>
+        <v>81</v>
       </c>
       <c r="D44" s="4" t="s">
-        <v>89</v>
+        <v>85</v>
       </c>
       <c r="E44" s="4"/>
       <c r="F44" s="4" t="s">
-        <v>52</v>
+        <v>21</v>
       </c>
       <c r="G44" s="4"/>
       <c r="H44" s="4"/>
       <c r="I44" s="4"/>
       <c r="J44" s="4"/>
-      <c r="K44" s="4" t="s">
-        <v>90</v>
-      </c>
+      <c r="K44" s="4"/>
     </row>
     <row r="45" spans="1:11" ht="15" x14ac:dyDescent="0.25">
-      <c r="A45" s="4">
+      <c r="A45" s="22">
         <v>44</v>
       </c>
       <c r="B45" s="4" t="s">
-        <v>91</v>
+        <v>86</v>
       </c>
       <c r="C45" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="D45" s="4" t="s">
         <v>88</v>
-      </c>
-      <c r="D45" s="4" t="s">
-        <v>92</v>
       </c>
       <c r="E45" s="4"/>
       <c r="F45" s="4" t="s">
@@ -2968,21 +2994,21 @@
       <c r="I45" s="4"/>
       <c r="J45" s="4"/>
       <c r="K45" s="4" t="s">
-        <v>93</v>
+        <v>89</v>
       </c>
     </row>
     <row r="46" spans="1:11" ht="15" x14ac:dyDescent="0.25">
-      <c r="A46" s="4">
+      <c r="A46" s="22">
         <v>45</v>
       </c>
       <c r="B46" s="4" t="s">
-        <v>94</v>
+        <v>90</v>
       </c>
       <c r="C46" s="4" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="D46" s="4" t="s">
-        <v>95</v>
+        <v>91</v>
       </c>
       <c r="E46" s="4"/>
       <c r="F46" s="4" t="s">
@@ -2993,21 +3019,21 @@
       <c r="I46" s="4"/>
       <c r="J46" s="4"/>
       <c r="K46" s="4" t="s">
-        <v>96</v>
+        <v>92</v>
       </c>
     </row>
     <row r="47" spans="1:11" ht="15" x14ac:dyDescent="0.25">
-      <c r="A47" s="4">
+      <c r="A47" s="22">
         <v>46</v>
       </c>
       <c r="B47" s="4" t="s">
-        <v>97</v>
+        <v>93</v>
       </c>
       <c r="C47" s="4" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="D47" s="4" t="s">
-        <v>98</v>
+        <v>94</v>
       </c>
       <c r="E47" s="4"/>
       <c r="F47" s="4" t="s">
@@ -3018,67 +3044,67 @@
       <c r="I47" s="4"/>
       <c r="J47" s="4"/>
       <c r="K47" s="4" t="s">
-        <v>99</v>
+        <v>95</v>
       </c>
     </row>
     <row r="48" spans="1:11" ht="15" x14ac:dyDescent="0.25">
-      <c r="A48" s="4">
+      <c r="A48" s="22">
         <v>47</v>
       </c>
       <c r="B48" s="4" t="s">
-        <v>347</v>
-      </c>
-      <c r="C48" s="4"/>
-      <c r="D48" s="4"/>
+        <v>96</v>
+      </c>
+      <c r="C48" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="D48" s="4" t="s">
+        <v>97</v>
+      </c>
       <c r="E48" s="4"/>
       <c r="F48" s="4" t="s">
-        <v>346</v>
+        <v>52</v>
       </c>
       <c r="G48" s="4"/>
       <c r="H48" s="4"/>
       <c r="I48" s="4"/>
-      <c r="J48" s="4" t="s">
-        <v>348</v>
-      </c>
-      <c r="K48" s="4"/>
+      <c r="J48" s="4"/>
+      <c r="K48" s="4" t="s">
+        <v>98</v>
+      </c>
     </row>
     <row r="49" spans="1:11" ht="15" x14ac:dyDescent="0.25">
-      <c r="A49" s="4">
+      <c r="A49" s="22">
         <v>48</v>
       </c>
       <c r="B49" s="4" t="s">
-        <v>338</v>
-      </c>
-      <c r="C49" s="4" t="s">
-        <v>88</v>
-      </c>
-      <c r="D49" s="4" t="s">
-        <v>339</v>
-      </c>
+        <v>336</v>
+      </c>
+      <c r="C49" s="4"/>
+      <c r="D49" s="4"/>
       <c r="E49" s="4"/>
       <c r="F49" s="4" t="s">
-        <v>14</v>
+        <v>335</v>
       </c>
       <c r="G49" s="4"/>
       <c r="H49" s="4"/>
       <c r="I49" s="4"/>
       <c r="J49" s="4" t="s">
-        <v>349</v>
+        <v>337</v>
       </c>
       <c r="K49" s="4"/>
     </row>
     <row r="50" spans="1:11" ht="15" x14ac:dyDescent="0.25">
-      <c r="A50" s="4">
+      <c r="A50" s="22">
         <v>49</v>
       </c>
       <c r="B50" s="4" t="s">
-        <v>340</v>
+        <v>327</v>
       </c>
       <c r="C50" s="4" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="D50" s="4" t="s">
-        <v>341</v>
+        <v>328</v>
       </c>
       <c r="E50" s="4"/>
       <c r="F50" s="4" t="s">
@@ -3088,118 +3114,120 @@
       <c r="H50" s="4"/>
       <c r="I50" s="4"/>
       <c r="J50" s="4" t="s">
-        <v>349</v>
+        <v>338</v>
       </c>
       <c r="K50" s="4"/>
     </row>
     <row r="51" spans="1:11" ht="15" x14ac:dyDescent="0.25">
-      <c r="A51" s="4">
+      <c r="A51" s="22">
         <v>50</v>
       </c>
       <c r="B51" s="4" t="s">
-        <v>342</v>
+        <v>329</v>
       </c>
       <c r="C51" s="4" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="D51" s="4" t="s">
-        <v>343</v>
+        <v>330</v>
       </c>
       <c r="E51" s="4"/>
       <c r="F51" s="4" t="s">
-        <v>52</v>
+        <v>14</v>
       </c>
       <c r="G51" s="4"/>
       <c r="H51" s="4"/>
       <c r="I51" s="4"/>
       <c r="J51" s="4" t="s">
-        <v>344</v>
+        <v>338</v>
       </c>
       <c r="K51" s="4"/>
     </row>
     <row r="52" spans="1:11" ht="15" x14ac:dyDescent="0.25">
-      <c r="A52" s="4">
+      <c r="A52" s="22">
         <v>51</v>
       </c>
       <c r="B52" s="4" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="C52" s="4" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="D52" s="4" t="s">
-        <v>132</v>
+        <v>332</v>
       </c>
       <c r="E52" s="4"/>
       <c r="F52" s="4" t="s">
-        <v>21</v>
+        <v>52</v>
       </c>
       <c r="G52" s="4"/>
       <c r="H52" s="4"/>
       <c r="I52" s="4"/>
-      <c r="J52" s="4"/>
+      <c r="J52" s="4" t="s">
+        <v>333</v>
+      </c>
       <c r="K52" s="4"/>
     </row>
     <row r="53" spans="1:11" ht="15" x14ac:dyDescent="0.25">
-      <c r="A53" s="4">
+      <c r="A53" s="22">
         <v>52</v>
       </c>
       <c r="B53" s="4" t="s">
-        <v>331</v>
+        <v>319</v>
       </c>
       <c r="C53" s="4" t="s">
-        <v>345</v>
+        <v>87</v>
       </c>
       <c r="D53" s="4" t="s">
-        <v>135</v>
+        <v>126</v>
       </c>
       <c r="E53" s="4"/>
       <c r="F53" s="4" t="s">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="G53" s="4"/>
       <c r="H53" s="4"/>
       <c r="I53" s="4"/>
-      <c r="J53" s="7" t="s">
-        <v>353</v>
-      </c>
+      <c r="J53" s="4"/>
       <c r="K53" s="4"/>
     </row>
     <row r="54" spans="1:11" ht="15" x14ac:dyDescent="0.25">
-      <c r="A54" s="4">
+      <c r="A54" s="22">
         <v>53</v>
       </c>
       <c r="B54" s="4" t="s">
-        <v>332</v>
+        <v>320</v>
       </c>
       <c r="C54" s="4" t="s">
-        <v>345</v>
+        <v>334</v>
       </c>
       <c r="D54" s="4" t="s">
-        <v>59</v>
+        <v>127</v>
       </c>
       <c r="E54" s="4"/>
       <c r="F54" s="4" t="s">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="G54" s="4"/>
       <c r="H54" s="4"/>
       <c r="I54" s="4"/>
-      <c r="J54" s="4"/>
+      <c r="J54" s="32">
+        <v>996289289033</v>
+      </c>
       <c r="K54" s="4"/>
     </row>
     <row r="55" spans="1:11" ht="15" x14ac:dyDescent="0.25">
-      <c r="A55" s="4">
+      <c r="A55" s="22">
         <v>54</v>
       </c>
       <c r="B55" s="4" t="s">
-        <v>333</v>
+        <v>321</v>
       </c>
       <c r="C55" s="4" t="s">
-        <v>345</v>
+        <v>334</v>
       </c>
       <c r="D55" s="4" t="s">
-        <v>139</v>
+        <v>58</v>
       </c>
       <c r="E55" s="4"/>
       <c r="F55" s="4" t="s">
@@ -3212,1833 +3240,2044 @@
       <c r="K55" s="4"/>
     </row>
     <row r="56" spans="1:11" ht="15" x14ac:dyDescent="0.25">
-      <c r="A56" s="4">
+      <c r="A56" s="22">
         <v>55</v>
       </c>
       <c r="B56" s="4" t="s">
-        <v>354</v>
-      </c>
-      <c r="C56" s="2" t="s">
+        <v>322</v>
+      </c>
+      <c r="C56" s="4" t="s">
+        <v>334</v>
+      </c>
+      <c r="D56" s="4" t="s">
+        <v>129</v>
+      </c>
+      <c r="E56" s="4"/>
+      <c r="F56" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="G56" s="4"/>
+      <c r="H56" s="4"/>
+      <c r="I56" s="4"/>
+      <c r="J56" s="4"/>
+      <c r="K56" s="4"/>
+    </row>
+    <row r="57" spans="1:11" ht="15" x14ac:dyDescent="0.25">
+      <c r="A57" s="22">
+        <v>56</v>
+      </c>
+      <c r="B57" s="4" t="s">
+        <v>342</v>
+      </c>
+      <c r="C57" s="4" t="s">
+        <v>69</v>
+      </c>
+      <c r="D57" s="4" t="s">
+        <v>99</v>
+      </c>
+      <c r="E57" s="4"/>
+      <c r="F57" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="G57" s="4"/>
+      <c r="H57" s="4"/>
+      <c r="I57" s="4"/>
+      <c r="J57" s="4"/>
+      <c r="K57" s="4"/>
+    </row>
+    <row r="58" spans="1:11" ht="15" x14ac:dyDescent="0.25">
+      <c r="A58" s="22">
+        <v>57</v>
+      </c>
+      <c r="B58" s="4" t="s">
+        <v>306</v>
+      </c>
+      <c r="C58" s="4" t="s">
+        <v>69</v>
+      </c>
+      <c r="D58" s="4"/>
+      <c r="E58" s="4"/>
+      <c r="F58" s="4" t="s">
+        <v>307</v>
+      </c>
+      <c r="G58" s="4"/>
+      <c r="H58" s="4"/>
+      <c r="I58" s="4"/>
+      <c r="J58" s="4">
+        <v>5</v>
+      </c>
+      <c r="K58" s="4"/>
+    </row>
+    <row r="59" spans="1:11" ht="15" x14ac:dyDescent="0.25">
+      <c r="A59" s="22">
+        <v>58</v>
+      </c>
+      <c r="B59" s="4" t="s">
+        <v>336</v>
+      </c>
+      <c r="C59" s="4"/>
+      <c r="D59" s="4"/>
+      <c r="E59" s="4"/>
+      <c r="F59" s="4" t="s">
+        <v>335</v>
+      </c>
+      <c r="G59" s="4"/>
+      <c r="H59" s="4"/>
+      <c r="I59" s="4"/>
+      <c r="J59" s="4" t="s">
+        <v>337</v>
+      </c>
+      <c r="K59" s="4"/>
+    </row>
+    <row r="60" spans="1:11" ht="15" x14ac:dyDescent="0.25">
+      <c r="A60" s="22">
+        <v>59</v>
+      </c>
+      <c r="B60" s="4" t="s">
+        <v>339</v>
+      </c>
+      <c r="C60" s="4" t="s">
+        <v>346</v>
+      </c>
+      <c r="D60" s="4" t="s">
+        <v>340</v>
+      </c>
+      <c r="E60" s="4"/>
+      <c r="F60" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="G60" s="4"/>
+      <c r="H60" s="4"/>
+      <c r="I60" s="4"/>
+      <c r="J60" s="4" t="s">
+        <v>338</v>
+      </c>
+      <c r="K60" s="4"/>
+    </row>
+    <row r="61" spans="1:11" ht="15" x14ac:dyDescent="0.25">
+      <c r="A61" s="22">
+        <v>60</v>
+      </c>
+      <c r="B61" s="4" t="s">
+        <v>306</v>
+      </c>
+      <c r="C61" s="4" t="s">
+        <v>346</v>
+      </c>
+      <c r="D61" s="4"/>
+      <c r="E61" s="4"/>
+      <c r="F61" s="4" t="s">
+        <v>307</v>
+      </c>
+      <c r="G61" s="4"/>
+      <c r="H61" s="4"/>
+      <c r="I61" s="4"/>
+      <c r="J61" s="4">
+        <v>5</v>
+      </c>
+      <c r="K61" s="4"/>
+    </row>
+    <row r="62" spans="1:11" ht="15" x14ac:dyDescent="0.25">
+      <c r="A62" s="22">
+        <v>61</v>
+      </c>
+      <c r="B62" s="4" t="s">
+        <v>341</v>
+      </c>
+      <c r="C62" s="4" t="s">
+        <v>346</v>
+      </c>
+      <c r="D62" s="4" t="s">
+        <v>347</v>
+      </c>
+      <c r="E62" s="4"/>
+      <c r="F62" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="G62" s="4"/>
+      <c r="H62" s="4"/>
+      <c r="I62" s="4"/>
+      <c r="J62" s="4"/>
+      <c r="K62" s="4"/>
+    </row>
+    <row r="63" spans="1:11" s="2" customFormat="1" ht="15" x14ac:dyDescent="0.25">
+      <c r="A63" s="22">
+        <v>62</v>
+      </c>
+      <c r="B63" s="4" t="s">
+        <v>306</v>
+      </c>
+      <c r="C63" s="4" t="s">
+        <v>69</v>
+      </c>
+      <c r="D63" s="4"/>
+      <c r="E63" s="4"/>
+      <c r="F63" s="4" t="s">
+        <v>307</v>
+      </c>
+      <c r="G63" s="4"/>
+      <c r="H63" s="4"/>
+      <c r="I63" s="4"/>
+      <c r="J63" s="4"/>
+      <c r="K63" s="4"/>
+    </row>
+    <row r="64" spans="1:11" s="9" customFormat="1" ht="15" x14ac:dyDescent="0.25">
+      <c r="A64" s="22">
+        <v>63</v>
+      </c>
+      <c r="B64" s="13" t="s">
+        <v>345</v>
+      </c>
+      <c r="C64" s="13" t="s">
+        <v>69</v>
+      </c>
+      <c r="D64" s="13" t="s">
+        <v>343</v>
+      </c>
+      <c r="E64" s="13"/>
+      <c r="F64" s="13" t="s">
+        <v>21</v>
+      </c>
+      <c r="G64" s="13"/>
+      <c r="H64" s="13"/>
+      <c r="I64" s="13"/>
+      <c r="J64" s="13"/>
+      <c r="K64" s="13"/>
+    </row>
+    <row r="65" spans="1:11" s="2" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A65" s="22">
+        <v>64</v>
+      </c>
+      <c r="B65" s="4" t="s">
+        <v>306</v>
+      </c>
+      <c r="C65" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="D65" s="4"/>
+      <c r="E65" s="4"/>
+      <c r="F65" s="4" t="s">
+        <v>348</v>
+      </c>
+      <c r="G65" s="4"/>
+      <c r="H65" s="4"/>
+      <c r="I65" s="4"/>
+      <c r="J65" s="4"/>
+      <c r="K65" s="4"/>
+    </row>
+    <row r="66" spans="1:11" s="2" customFormat="1" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A66" s="22">
+        <v>65</v>
+      </c>
+      <c r="B66" s="4" t="s">
+        <v>352</v>
+      </c>
+      <c r="C66" s="20" t="s">
+        <v>100</v>
+      </c>
+      <c r="D66" s="21" t="s">
+        <v>36</v>
+      </c>
+      <c r="E66" s="4"/>
+      <c r="F66" s="4" t="s">
+        <v>307</v>
+      </c>
+      <c r="G66" s="4"/>
+      <c r="H66" s="4"/>
+      <c r="I66" s="4"/>
+      <c r="J66" s="4"/>
+      <c r="K66" s="4"/>
+    </row>
+    <row r="67" spans="1:11" s="2" customFormat="1" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A67" s="22">
+        <v>66</v>
+      </c>
+      <c r="B67" s="4" t="s">
+        <v>358</v>
+      </c>
+      <c r="C67" s="20"/>
+      <c r="D67" s="21"/>
+      <c r="E67" s="4"/>
+      <c r="F67" s="4" t="s">
+        <v>359</v>
+      </c>
+      <c r="G67" s="4"/>
+      <c r="H67" s="4"/>
+      <c r="I67" s="4"/>
+      <c r="J67" s="4" t="s">
+        <v>360</v>
+      </c>
+      <c r="K67" s="4"/>
+    </row>
+    <row r="68" spans="1:11" s="2" customFormat="1" ht="15" x14ac:dyDescent="0.25">
+      <c r="A68" s="22">
+        <v>67</v>
+      </c>
+      <c r="B68" s="4" t="s">
+        <v>352</v>
+      </c>
+      <c r="C68" s="20" t="s">
+        <v>100</v>
+      </c>
+      <c r="D68" s="21" t="s">
+        <v>36</v>
+      </c>
+      <c r="E68" s="4"/>
+      <c r="F68" s="4" t="s">
+        <v>362</v>
+      </c>
+      <c r="G68" s="4"/>
+      <c r="H68" s="4"/>
+      <c r="I68" s="4" t="s">
+        <v>357</v>
+      </c>
+      <c r="J68" s="4" t="s">
+        <v>361</v>
+      </c>
+      <c r="K68" s="4"/>
+    </row>
+    <row r="69" spans="1:11" s="2" customFormat="1" ht="15" x14ac:dyDescent="0.25">
+      <c r="A69" s="22">
+        <v>68</v>
+      </c>
+      <c r="B69" s="4" t="s">
+        <v>306</v>
+      </c>
+      <c r="C69" s="20" t="s">
+        <v>100</v>
+      </c>
+      <c r="D69" s="4"/>
+      <c r="E69" s="4"/>
+      <c r="F69" s="4" t="s">
+        <v>307</v>
+      </c>
+      <c r="G69" s="4"/>
+      <c r="H69" s="4"/>
+      <c r="I69" s="4"/>
+      <c r="J69" s="4"/>
+      <c r="K69" s="4"/>
+    </row>
+    <row r="70" spans="1:11" s="9" customFormat="1" ht="15" x14ac:dyDescent="0.25">
+      <c r="A70" s="22">
+        <v>69</v>
+      </c>
+      <c r="B70" s="13" t="s">
+        <v>364</v>
+      </c>
+      <c r="C70" s="13" t="s">
+        <v>369</v>
+      </c>
+      <c r="D70" s="20" t="s">
+        <v>363</v>
+      </c>
+      <c r="E70" s="13"/>
+      <c r="F70" s="13" t="s">
+        <v>21</v>
+      </c>
+      <c r="G70" s="13"/>
+      <c r="H70" s="13"/>
+      <c r="I70" s="13"/>
+      <c r="J70" s="13"/>
+      <c r="K70" s="13"/>
+    </row>
+    <row r="71" spans="1:11" s="9" customFormat="1" ht="15" x14ac:dyDescent="0.25">
+      <c r="A71" s="22">
         <v>70</v>
       </c>
-      <c r="D56" s="2" t="s">
+      <c r="B71" s="13" t="s">
+        <v>367</v>
+      </c>
+      <c r="C71" s="13" t="s">
+        <v>371</v>
+      </c>
+      <c r="D71" s="13" t="s">
+        <v>365</v>
+      </c>
+      <c r="E71" s="13"/>
+      <c r="F71" s="13" t="s">
+        <v>21</v>
+      </c>
+      <c r="G71" s="13"/>
+      <c r="H71" s="13"/>
+      <c r="I71" s="13"/>
+      <c r="J71" s="13"/>
+      <c r="K71" s="13"/>
+    </row>
+    <row r="72" spans="1:11" s="2" customFormat="1" ht="15" x14ac:dyDescent="0.25">
+      <c r="A72" s="22">
+        <v>71</v>
+      </c>
+      <c r="B72" s="4" t="s">
+        <v>306</v>
+      </c>
+      <c r="C72" s="13" t="s">
+        <v>371</v>
+      </c>
+      <c r="D72" s="4"/>
+      <c r="E72" s="4"/>
+      <c r="F72" s="4" t="s">
+        <v>307</v>
+      </c>
+      <c r="G72" s="4"/>
+      <c r="H72" s="4"/>
+      <c r="I72" s="4"/>
+      <c r="J72" s="13">
+        <v>30</v>
+      </c>
+      <c r="K72" s="4"/>
+    </row>
+    <row r="73" spans="1:11" s="2" customFormat="1" ht="15" x14ac:dyDescent="0.25">
+      <c r="A73" s="22">
+        <v>72</v>
+      </c>
+      <c r="B73" s="4" t="s">
+        <v>368</v>
+      </c>
+      <c r="C73" s="21" t="s">
+        <v>369</v>
+      </c>
+      <c r="D73" s="4" t="s">
+        <v>366</v>
+      </c>
+      <c r="E73" s="4"/>
+      <c r="F73" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="G73" s="4"/>
+      <c r="H73" s="4"/>
+      <c r="I73" s="4"/>
+      <c r="J73" s="4"/>
+      <c r="K73" s="4"/>
+    </row>
+    <row r="74" spans="1:11" s="2" customFormat="1" ht="15" x14ac:dyDescent="0.25">
+      <c r="A74" s="22">
+        <v>73</v>
+      </c>
+      <c r="B74" s="4" t="s">
+        <v>306</v>
+      </c>
+      <c r="C74" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="E74" s="4"/>
+      <c r="F74" s="4" t="s">
+        <v>307</v>
+      </c>
+      <c r="G74" s="4"/>
+      <c r="H74" s="4"/>
+      <c r="I74" s="4"/>
+      <c r="J74" s="4">
+        <v>30</v>
+      </c>
+      <c r="K74" s="4"/>
+    </row>
+    <row r="75" spans="1:11" s="2" customFormat="1" ht="15" x14ac:dyDescent="0.25">
+      <c r="A75" s="22">
+        <v>74</v>
+      </c>
+      <c r="B75" s="4" t="s">
+        <v>104</v>
+      </c>
+      <c r="C75" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="D75" s="4" t="s">
+        <v>105</v>
+      </c>
+      <c r="E75" s="4"/>
+      <c r="F75" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="G75" s="4"/>
+      <c r="H75" s="4"/>
+      <c r="I75" s="4"/>
+      <c r="J75" s="4"/>
+      <c r="K75" s="4"/>
+    </row>
+    <row r="76" spans="1:11" s="2" customFormat="1" ht="15" x14ac:dyDescent="0.25">
+      <c r="A76" s="22">
+        <v>75</v>
+      </c>
+      <c r="B76" s="4" t="s">
+        <v>106</v>
+      </c>
+      <c r="C76" s="4" t="s">
+        <v>107</v>
+      </c>
+      <c r="D76" s="4" t="s">
+        <v>108</v>
+      </c>
+      <c r="E76" s="4"/>
+      <c r="F76" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="G76" s="4"/>
+      <c r="H76" s="4"/>
+      <c r="I76" s="4"/>
+      <c r="J76" s="4" t="s">
+        <v>373</v>
+      </c>
+      <c r="K76" s="4"/>
+    </row>
+    <row r="77" spans="1:11" s="2" customFormat="1" ht="15" x14ac:dyDescent="0.25">
+      <c r="A77" s="22">
+        <v>76</v>
+      </c>
+      <c r="B77" s="4" t="s">
+        <v>110</v>
+      </c>
+      <c r="C77" s="4" t="s">
+        <v>107</v>
+      </c>
+      <c r="D77" s="4" t="s">
+        <v>111</v>
+      </c>
+      <c r="E77" s="4"/>
+      <c r="F77" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="G77" s="4"/>
+      <c r="H77" s="4"/>
+      <c r="I77" s="4"/>
+      <c r="J77" s="4" t="s">
+        <v>252</v>
+      </c>
+      <c r="K77" s="4"/>
+    </row>
+    <row r="78" spans="1:11" s="2" customFormat="1" ht="15" x14ac:dyDescent="0.25">
+      <c r="A78" s="22">
+        <v>77</v>
+      </c>
+      <c r="B78" s="4" t="s">
+        <v>113</v>
+      </c>
+      <c r="C78" s="4" t="s">
+        <v>107</v>
+      </c>
+      <c r="D78" s="4" t="s">
+        <v>99</v>
+      </c>
+      <c r="E78" s="4"/>
+      <c r="F78" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="G78" s="4"/>
+      <c r="H78" s="4"/>
+      <c r="I78" s="4"/>
+      <c r="J78" s="4"/>
+      <c r="K78" s="4"/>
+    </row>
+    <row r="79" spans="1:11" s="2" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A79" s="22">
+        <v>78</v>
+      </c>
+      <c r="B79" s="4" t="s">
+        <v>306</v>
+      </c>
+      <c r="C79" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="D79" s="4"/>
+      <c r="E79" s="4"/>
+      <c r="F79" s="4" t="s">
+        <v>348</v>
+      </c>
+      <c r="G79" s="4"/>
+      <c r="H79" s="4"/>
+      <c r="I79" s="4"/>
+      <c r="J79" s="4"/>
+      <c r="K79" s="4"/>
+    </row>
+    <row r="80" spans="1:11" s="2" customFormat="1" ht="15" x14ac:dyDescent="0.25">
+      <c r="A80" s="22">
+        <v>79</v>
+      </c>
+      <c r="B80" s="4" t="s">
+        <v>372</v>
+      </c>
+      <c r="C80" s="20" t="s">
         <v>100</v>
       </c>
-      <c r="E56" s="4"/>
-      <c r="F56" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="G56" s="2"/>
-      <c r="H56" s="2"/>
-      <c r="I56" s="2"/>
-      <c r="J56" s="2"/>
-      <c r="K56" s="2"/>
-    </row>
-    <row r="57" spans="1:11" ht="15" x14ac:dyDescent="0.25">
-      <c r="A57" s="4">
-        <v>56</v>
-      </c>
-      <c r="B57" s="2" t="s">
-        <v>317</v>
-      </c>
-      <c r="C57" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="D57" s="2"/>
-      <c r="E57" s="2"/>
-      <c r="F57" s="4" t="s">
-        <v>318</v>
-      </c>
-      <c r="G57" s="2"/>
-      <c r="H57" s="2"/>
-      <c r="I57" s="2"/>
-      <c r="J57" s="2">
-        <v>10</v>
-      </c>
-      <c r="K57" s="2"/>
-    </row>
-    <row r="58" spans="1:11" ht="15" x14ac:dyDescent="0.25">
-      <c r="A58" s="4">
-        <v>57</v>
-      </c>
-      <c r="B58" s="2" t="s">
-        <v>347</v>
-      </c>
-      <c r="C58" s="2"/>
-      <c r="D58" s="2"/>
-      <c r="E58" s="2"/>
-      <c r="F58" s="2" t="s">
-        <v>346</v>
-      </c>
-      <c r="G58" s="2"/>
-      <c r="H58" s="2"/>
-      <c r="I58" s="2"/>
-      <c r="J58" s="2" t="s">
+      <c r="D80" s="21" t="s">
+        <v>36</v>
+      </c>
+      <c r="E80" s="4"/>
+      <c r="F80" s="4" t="s">
+        <v>362</v>
+      </c>
+      <c r="G80" s="4"/>
+      <c r="H80" s="4"/>
+      <c r="I80" s="4" t="s">
+        <v>357</v>
+      </c>
+      <c r="J80" s="4" t="s">
+        <v>361</v>
+      </c>
+      <c r="K80" s="4"/>
+    </row>
+    <row r="81" spans="1:11" s="2" customFormat="1" ht="15" x14ac:dyDescent="0.25">
+      <c r="A81" s="22">
+        <v>80</v>
+      </c>
+      <c r="B81" s="4" t="s">
+        <v>379</v>
+      </c>
+      <c r="C81" s="20" t="s">
+        <v>100</v>
+      </c>
+      <c r="D81" s="4"/>
+      <c r="E81" s="4"/>
+      <c r="F81" s="4" t="s">
         <v>348</v>
       </c>
-      <c r="K58" s="2"/>
-    </row>
-    <row r="59" spans="1:11" ht="15" x14ac:dyDescent="0.25">
-      <c r="A59" s="4">
-        <v>58</v>
-      </c>
-      <c r="B59" s="2" t="s">
-        <v>350</v>
-      </c>
-      <c r="C59" s="2" t="s">
-        <v>358</v>
-      </c>
-      <c r="D59" s="2" t="s">
-        <v>351</v>
-      </c>
-      <c r="E59" s="2"/>
-      <c r="F59" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="G59" s="2"/>
-      <c r="H59" s="2"/>
-      <c r="I59" s="2"/>
-      <c r="J59" s="2" t="s">
-        <v>349</v>
-      </c>
-      <c r="K59" s="2"/>
-    </row>
-    <row r="60" spans="1:11" ht="15" x14ac:dyDescent="0.25">
-      <c r="A60" s="4">
-        <v>59</v>
-      </c>
-      <c r="B60" s="2" t="s">
-        <v>317</v>
-      </c>
-      <c r="C60" s="2" t="s">
-        <v>358</v>
-      </c>
-      <c r="D60" s="2"/>
-      <c r="E60" s="2"/>
-      <c r="F60" s="2" t="s">
-        <v>318</v>
-      </c>
-      <c r="G60" s="2"/>
-      <c r="H60" s="2"/>
-      <c r="I60" s="2"/>
-      <c r="J60" s="2">
-        <v>10</v>
-      </c>
-      <c r="K60" s="2"/>
-    </row>
-    <row r="61" spans="1:11" ht="15" x14ac:dyDescent="0.25">
-      <c r="A61" s="4">
-        <v>60</v>
-      </c>
-      <c r="B61" s="2" t="s">
-        <v>352</v>
-      </c>
-      <c r="C61" s="2" t="s">
-        <v>358</v>
-      </c>
-      <c r="D61" s="2" t="s">
-        <v>359</v>
-      </c>
-      <c r="E61" s="2"/>
-      <c r="F61" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="G61" s="2"/>
-      <c r="H61" s="2"/>
-      <c r="I61" s="2"/>
-      <c r="J61" s="2"/>
-      <c r="K61" s="2"/>
-    </row>
-    <row r="62" spans="1:11" s="2" customFormat="1" ht="15" x14ac:dyDescent="0.25">
-      <c r="A62" s="4">
-        <v>61</v>
-      </c>
-      <c r="B62" s="2" t="s">
-        <v>317</v>
-      </c>
-      <c r="C62" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="F62" s="2" t="s">
-        <v>318</v>
-      </c>
-    </row>
-    <row r="63" spans="1:11" s="11" customFormat="1" ht="15" x14ac:dyDescent="0.25">
-      <c r="A63" s="4">
-        <v>62</v>
-      </c>
-      <c r="B63" s="11" t="s">
-        <v>357</v>
-      </c>
-      <c r="C63" s="11" t="s">
-        <v>70</v>
-      </c>
-      <c r="D63" s="11" t="s">
-        <v>355</v>
-      </c>
-      <c r="F63" s="11" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="64" spans="1:11" s="2" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A64" s="4">
-        <v>63</v>
-      </c>
-      <c r="B64" s="2" t="s">
-        <v>317</v>
-      </c>
-      <c r="C64" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="F64" s="2" t="s">
-        <v>360</v>
-      </c>
-    </row>
-    <row r="65" spans="1:11" s="2" customFormat="1" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A65" s="4">
-        <v>64</v>
-      </c>
-      <c r="B65" s="2" t="s">
-        <v>364</v>
-      </c>
-      <c r="C65" s="12" t="s">
-        <v>101</v>
-      </c>
-      <c r="D65" s="13" t="s">
-        <v>36</v>
-      </c>
-      <c r="F65" s="2" t="s">
-        <v>318</v>
-      </c>
-    </row>
-    <row r="66" spans="1:11" s="2" customFormat="1" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A66" s="4">
-        <v>65</v>
-      </c>
-      <c r="B66" s="2" t="s">
-        <v>370</v>
-      </c>
-      <c r="C66" s="12"/>
-      <c r="D66" s="13"/>
-      <c r="F66" s="2" t="s">
-        <v>371</v>
-      </c>
-      <c r="J66" s="2" t="s">
-        <v>372</v>
-      </c>
-    </row>
-    <row r="67" spans="1:11" s="2" customFormat="1" ht="15" x14ac:dyDescent="0.25">
-      <c r="A67" s="4">
-        <v>66</v>
-      </c>
-      <c r="B67" s="2" t="s">
-        <v>364</v>
-      </c>
-      <c r="C67" s="12" t="s">
-        <v>101</v>
-      </c>
-      <c r="D67" s="13" t="s">
-        <v>36</v>
-      </c>
-      <c r="F67" s="2" t="s">
-        <v>374</v>
-      </c>
-      <c r="I67" s="2" t="s">
-        <v>369</v>
-      </c>
-      <c r="J67" s="2" t="s">
-        <v>373</v>
-      </c>
-    </row>
-    <row r="68" spans="1:11" s="2" customFormat="1" ht="15" x14ac:dyDescent="0.25">
-      <c r="A68" s="4">
-        <v>67</v>
-      </c>
-      <c r="B68" s="2" t="s">
-        <v>317</v>
-      </c>
-      <c r="C68" s="12" t="s">
-        <v>101</v>
-      </c>
-      <c r="F68" s="2" t="s">
-        <v>318</v>
-      </c>
-    </row>
-    <row r="69" spans="1:11" s="11" customFormat="1" ht="15" x14ac:dyDescent="0.25">
-      <c r="A69" s="4">
-        <v>68</v>
-      </c>
-      <c r="B69" s="11" t="s">
-        <v>376</v>
-      </c>
-      <c r="C69" s="25" t="s">
-        <v>387</v>
-      </c>
-      <c r="D69" s="12" t="s">
-        <v>375</v>
-      </c>
-      <c r="F69" s="11" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="70" spans="1:11" s="11" customFormat="1" ht="15" x14ac:dyDescent="0.25">
-      <c r="A70" s="4">
-        <v>69</v>
-      </c>
-      <c r="B70" s="11" t="s">
-        <v>384</v>
-      </c>
-      <c r="C70" s="25" t="s">
-        <v>389</v>
-      </c>
-      <c r="D70" s="11" t="s">
+      <c r="G81" s="4"/>
+      <c r="H81" s="4"/>
+      <c r="I81" s="4"/>
+      <c r="J81" s="4"/>
+      <c r="K81" s="4"/>
+    </row>
+    <row r="82" spans="1:11" s="2" customFormat="1" ht="15" x14ac:dyDescent="0.25">
+      <c r="A82" s="22">
+        <v>81</v>
+      </c>
+      <c r="B82" s="4" t="s">
         <v>380</v>
       </c>
-      <c r="F70" s="11" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="71" spans="1:11" s="2" customFormat="1" ht="15" x14ac:dyDescent="0.25">
-      <c r="A71" s="4">
-        <v>70</v>
-      </c>
-      <c r="B71" s="2" t="s">
-        <v>317</v>
-      </c>
-      <c r="C71" s="25" t="s">
-        <v>389</v>
-      </c>
-      <c r="F71" s="2" t="s">
-        <v>318</v>
-      </c>
-      <c r="J71" s="11">
-        <v>1000</v>
-      </c>
-    </row>
-    <row r="72" spans="1:11" s="11" customFormat="1" ht="15" x14ac:dyDescent="0.25">
-      <c r="A72" s="4">
-        <v>71</v>
-      </c>
-      <c r="B72" s="11" t="s">
-        <v>379</v>
-      </c>
-      <c r="C72" s="25" t="s">
-        <v>389</v>
-      </c>
-      <c r="D72" s="12" t="s">
-        <v>381</v>
-      </c>
-      <c r="F72" s="11" t="s">
-        <v>390</v>
-      </c>
-      <c r="G72" s="11" t="s">
-        <v>391</v>
-      </c>
-      <c r="H72" s="11" t="s">
-        <v>392</v>
-      </c>
-      <c r="J72" s="11" t="s">
-        <v>385</v>
-      </c>
-    </row>
-    <row r="73" spans="1:11" s="21" customFormat="1" ht="15" x14ac:dyDescent="0.25">
-      <c r="A73" s="4">
-        <v>72</v>
-      </c>
-      <c r="B73" s="21" t="s">
-        <v>386</v>
-      </c>
-      <c r="C73" s="22" t="s">
-        <v>387</v>
-      </c>
-      <c r="D73" s="21" t="s">
-        <v>382</v>
-      </c>
-      <c r="F73" s="21" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="74" spans="1:11" s="24" customFormat="1" ht="15" x14ac:dyDescent="0.25">
-      <c r="A74" s="4">
-        <v>73</v>
-      </c>
-      <c r="B74" s="24" t="s">
-        <v>317</v>
-      </c>
-      <c r="C74" s="23" t="s">
-        <v>101</v>
-      </c>
-      <c r="F74" s="24" t="s">
-        <v>318</v>
-      </c>
-    </row>
-    <row r="75" spans="1:11" s="21" customFormat="1" ht="15" x14ac:dyDescent="0.25">
-      <c r="A75" s="4">
-        <v>74</v>
-      </c>
-      <c r="B75" s="21" t="s">
-        <v>105</v>
-      </c>
-      <c r="C75" s="23" t="s">
-        <v>101</v>
-      </c>
-      <c r="D75" s="21" t="s">
-        <v>106</v>
-      </c>
-      <c r="F75" s="21" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="76" spans="1:11" ht="15" x14ac:dyDescent="0.25">
-      <c r="A76" s="4">
-        <v>75</v>
-      </c>
-      <c r="B76" t="s">
-        <v>107</v>
-      </c>
-      <c r="C76" t="s">
-        <v>108</v>
-      </c>
-      <c r="D76" t="s">
-        <v>109</v>
-      </c>
-      <c r="F76" t="s">
-        <v>52</v>
-      </c>
-      <c r="K76" t="s">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="77" spans="1:11" ht="15" x14ac:dyDescent="0.25">
-      <c r="A77" s="4">
-        <v>76</v>
-      </c>
-      <c r="B77" t="s">
-        <v>111</v>
-      </c>
-      <c r="C77" t="s">
-        <v>108</v>
-      </c>
-      <c r="D77" t="s">
-        <v>112</v>
-      </c>
-      <c r="F77" t="s">
-        <v>52</v>
-      </c>
-      <c r="K77" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="78" spans="1:11" ht="15" x14ac:dyDescent="0.25">
-      <c r="A78" s="4">
-        <v>77</v>
-      </c>
-      <c r="B78" t="s">
-        <v>114</v>
-      </c>
-      <c r="C78" t="s">
-        <v>108</v>
-      </c>
-      <c r="D78" t="s">
-        <v>100</v>
-      </c>
-      <c r="F78" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="79" spans="1:11" ht="15" x14ac:dyDescent="0.25">
-      <c r="A79" s="4">
-        <v>78</v>
-      </c>
-      <c r="B79" t="s">
-        <v>115</v>
-      </c>
-      <c r="C79" t="s">
-        <v>101</v>
-      </c>
-      <c r="D79" t="s">
-        <v>116</v>
-      </c>
-      <c r="F79" t="s">
-        <v>103</v>
-      </c>
-      <c r="G79" t="s">
-        <v>117</v>
-      </c>
-      <c r="H79" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="80" spans="1:11" ht="15" x14ac:dyDescent="0.25">
-      <c r="A80" s="4">
-        <v>79</v>
-      </c>
-      <c r="B80" t="s">
-        <v>118</v>
-      </c>
-      <c r="C80" t="s">
+      <c r="C82" s="6" t="s">
         <v>19</v>
       </c>
-      <c r="D80" t="s">
-        <v>39</v>
-      </c>
-      <c r="E80" t="s">
-        <v>119</v>
-      </c>
-      <c r="F80" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="81" spans="1:11" ht="15" x14ac:dyDescent="0.25">
-      <c r="A81" s="4">
-        <v>80</v>
-      </c>
-      <c r="B81" t="s">
-        <v>120</v>
-      </c>
-      <c r="C81" t="s">
-        <v>121</v>
-      </c>
-      <c r="D81" t="s">
-        <v>122</v>
-      </c>
-      <c r="F81" t="s">
-        <v>52</v>
-      </c>
-      <c r="K81" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="82" spans="1:11" ht="15" x14ac:dyDescent="0.25">
-      <c r="A82" s="4">
-        <v>81</v>
-      </c>
-      <c r="B82" t="s">
-        <v>124</v>
-      </c>
-      <c r="C82" t="s">
-        <v>121</v>
-      </c>
-      <c r="D82" t="s">
-        <v>125</v>
-      </c>
-      <c r="F82" t="s">
-        <v>52</v>
-      </c>
-      <c r="K82" t="s">
-        <v>126</v>
-      </c>
-    </row>
-    <row r="83" spans="1:11" ht="15" x14ac:dyDescent="0.25">
+      <c r="D82" s="4"/>
+      <c r="E82" s="4"/>
+      <c r="F82" s="4" t="s">
+        <v>348</v>
+      </c>
+      <c r="G82" s="4"/>
+      <c r="H82" s="4"/>
+      <c r="I82" s="4"/>
+      <c r="J82" s="4"/>
+      <c r="K82" s="4"/>
+    </row>
+    <row r="83" spans="1:11" s="2" customFormat="1" ht="15" x14ac:dyDescent="0.25">
       <c r="A83" s="4">
         <v>82</v>
       </c>
-      <c r="B83" t="s">
-        <v>127</v>
-      </c>
-      <c r="C83" t="s">
-        <v>121</v>
-      </c>
-      <c r="D83" t="s">
-        <v>128</v>
-      </c>
-      <c r="F83" t="s">
-        <v>52</v>
-      </c>
-      <c r="K83" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="84" spans="1:11" ht="15" x14ac:dyDescent="0.25">
+      <c r="B83" s="4" t="s">
+        <v>116</v>
+      </c>
+      <c r="C83" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="D83" s="21" t="s">
+        <v>381</v>
+      </c>
+      <c r="E83" s="4"/>
+      <c r="F83" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="G83" s="4"/>
+      <c r="H83" s="4"/>
+      <c r="I83" s="4"/>
+      <c r="J83" s="4"/>
+      <c r="K83" s="4"/>
+    </row>
+    <row r="84" spans="1:11" s="2" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A84" s="4">
         <v>83</v>
       </c>
-      <c r="B84" t="s">
-        <v>129</v>
-      </c>
-      <c r="C84" t="s">
-        <v>121</v>
-      </c>
-      <c r="D84" t="s">
-        <v>80</v>
-      </c>
-      <c r="F84" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="85" spans="1:11" ht="15" x14ac:dyDescent="0.25">
+      <c r="B84" s="4" t="s">
+        <v>306</v>
+      </c>
+      <c r="C84" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="D84" s="4"/>
+      <c r="E84" s="4"/>
+      <c r="F84" s="4" t="s">
+        <v>348</v>
+      </c>
+      <c r="G84" s="4"/>
+      <c r="H84" s="4"/>
+      <c r="I84" s="4"/>
+      <c r="J84" s="4"/>
+      <c r="K84" s="4"/>
+    </row>
+    <row r="85" spans="1:11" s="15" customFormat="1" ht="15" x14ac:dyDescent="0.25">
       <c r="A85" s="4">
         <v>84</v>
       </c>
-      <c r="B85" t="s">
-        <v>130</v>
-      </c>
-      <c r="C85" t="s">
-        <v>131</v>
-      </c>
-      <c r="D85" t="s">
-        <v>132</v>
-      </c>
-      <c r="F85" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="86" spans="1:11" ht="15" x14ac:dyDescent="0.25">
+      <c r="B85" s="13" t="s">
+        <v>375</v>
+      </c>
+      <c r="C85" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="D85" s="13"/>
+      <c r="E85" s="14"/>
+      <c r="F85" s="2" t="s">
+        <v>304</v>
+      </c>
+      <c r="G85" s="2"/>
+      <c r="H85" s="2"/>
+      <c r="I85" s="2"/>
+      <c r="J85" s="2" t="s">
+        <v>374</v>
+      </c>
+      <c r="K85" s="14"/>
+    </row>
+    <row r="86" spans="1:11" s="2" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A86" s="4">
         <v>85</v>
       </c>
-      <c r="B86" t="s">
-        <v>133</v>
-      </c>
-      <c r="C86" t="s">
-        <v>134</v>
-      </c>
-      <c r="D86" t="s">
-        <v>135</v>
-      </c>
-      <c r="F86" t="s">
-        <v>14</v>
-      </c>
-      <c r="K86" t="s">
-        <v>136</v>
-      </c>
-    </row>
-    <row r="87" spans="1:11" ht="15" x14ac:dyDescent="0.25">
+      <c r="B86" s="4" t="s">
+        <v>306</v>
+      </c>
+      <c r="C86" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="D86" s="4"/>
+      <c r="E86" s="4"/>
+      <c r="F86" s="4" t="s">
+        <v>348</v>
+      </c>
+      <c r="G86" s="4"/>
+      <c r="H86" s="4"/>
+      <c r="I86" s="4"/>
+      <c r="J86" s="4"/>
+      <c r="K86" s="4"/>
+    </row>
+    <row r="87" spans="1:11" s="2" customFormat="1" ht="15" x14ac:dyDescent="0.25">
       <c r="A87" s="4">
         <v>86</v>
       </c>
-      <c r="B87" t="s">
-        <v>137</v>
-      </c>
-      <c r="C87" t="s">
-        <v>134</v>
-      </c>
-      <c r="D87" t="s">
-        <v>59</v>
-      </c>
-      <c r="F87" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="88" spans="1:11" ht="15" x14ac:dyDescent="0.25">
+      <c r="B87" s="4" t="s">
+        <v>117</v>
+      </c>
+      <c r="C87" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="D87" s="4" t="s">
+        <v>118</v>
+      </c>
+      <c r="E87" s="4"/>
+      <c r="F87" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="G87" s="4"/>
+      <c r="H87" s="4"/>
+      <c r="I87" s="4"/>
+      <c r="J87" s="4" t="s">
+        <v>385</v>
+      </c>
+      <c r="K87" s="4"/>
+    </row>
+    <row r="88" spans="1:11" s="2" customFormat="1" ht="15" x14ac:dyDescent="0.25">
       <c r="A88" s="4">
         <v>87</v>
       </c>
-      <c r="B88" t="s">
+      <c r="B88" s="4" t="s">
+        <v>120</v>
+      </c>
+      <c r="C88" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="D88" s="4" t="s">
+        <v>121</v>
+      </c>
+      <c r="E88" s="4"/>
+      <c r="F88" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="G88" s="4"/>
+      <c r="H88" s="4"/>
+      <c r="I88" s="4"/>
+      <c r="J88" s="4" t="s">
+        <v>376</v>
+      </c>
+      <c r="K88" s="4"/>
+    </row>
+    <row r="89" spans="1:11" ht="19.5" x14ac:dyDescent="0.25">
+      <c r="A89" s="22">
+        <v>88</v>
+      </c>
+      <c r="B89" s="6" t="s">
+        <v>123</v>
+      </c>
+      <c r="C89" t="s">
+        <v>125</v>
+      </c>
+      <c r="D89" s="6" t="s">
+        <v>386</v>
+      </c>
+      <c r="E89" s="31"/>
+      <c r="F89" s="6" t="s">
+        <v>52</v>
+      </c>
+      <c r="J89" s="4" t="s">
+        <v>377</v>
+      </c>
+    </row>
+    <row r="90" spans="1:11" ht="15" x14ac:dyDescent="0.25">
+      <c r="A90" s="22">
+        <v>89</v>
+      </c>
+      <c r="B90" s="6" t="s">
+        <v>124</v>
+      </c>
+      <c r="C90" t="s">
+        <v>125</v>
+      </c>
+      <c r="D90" s="6" t="s">
+        <v>79</v>
+      </c>
+      <c r="F90" s="6" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="91" spans="1:11" s="29" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A91" s="22">
+        <v>90</v>
+      </c>
+      <c r="B91" s="22" t="s">
+        <v>306</v>
+      </c>
+      <c r="C91" t="s">
+        <v>125</v>
+      </c>
+      <c r="D91" s="22"/>
+      <c r="E91" s="22"/>
+      <c r="F91" s="4" t="s">
+        <v>348</v>
+      </c>
+      <c r="G91" s="22"/>
+      <c r="H91" s="22"/>
+      <c r="I91" s="22"/>
+      <c r="J91" s="4"/>
+      <c r="K91" s="22"/>
+    </row>
+    <row r="92" spans="1:11" ht="15" x14ac:dyDescent="0.25">
+      <c r="A92" s="22">
+        <v>91</v>
+      </c>
+      <c r="B92" s="6" t="s">
+        <v>130</v>
+      </c>
+      <c r="C92" s="6" t="s">
+        <v>125</v>
+      </c>
+      <c r="D92" s="6" t="s">
+        <v>131</v>
+      </c>
+      <c r="F92" s="6" t="s">
+        <v>52</v>
+      </c>
+      <c r="J92" s="4" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="93" spans="1:11" ht="15" x14ac:dyDescent="0.25">
+      <c r="A93" s="22">
+        <v>92</v>
+      </c>
+      <c r="B93" s="6" t="s">
+        <v>132</v>
+      </c>
+      <c r="C93" s="6" t="s">
+        <v>125</v>
+      </c>
+      <c r="D93" s="6" t="s">
+        <v>133</v>
+      </c>
+      <c r="F93" s="6" t="s">
+        <v>52</v>
+      </c>
+      <c r="J93" s="6" t="s">
+        <v>378</v>
+      </c>
+    </row>
+    <row r="94" spans="1:11" ht="15" x14ac:dyDescent="0.25">
+      <c r="A94" s="22">
+        <v>93</v>
+      </c>
+      <c r="B94" s="6" t="s">
+        <v>134</v>
+      </c>
+      <c r="C94" s="6" t="s">
+        <v>125</v>
+      </c>
+      <c r="D94" s="6" t="s">
+        <v>99</v>
+      </c>
+      <c r="F94" s="6" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="95" spans="1:11" ht="15" x14ac:dyDescent="0.25">
+      <c r="A95" s="22">
+        <v>94</v>
+      </c>
+      <c r="B95" s="6" t="s">
+        <v>135</v>
+      </c>
+      <c r="C95" s="6" t="s">
+        <v>136</v>
+      </c>
+      <c r="D95" s="6" t="s">
+        <v>137</v>
+      </c>
+      <c r="F95" s="6" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="96" spans="1:11" s="12" customFormat="1" ht="15" x14ac:dyDescent="0.25">
+      <c r="A96" s="22">
+        <v>95</v>
+      </c>
+      <c r="B96" s="24" t="s">
         <v>138</v>
       </c>
-      <c r="C88" t="s">
+      <c r="C96" s="24" t="s">
+        <v>136</v>
+      </c>
+      <c r="D96" s="24" t="s">
+        <v>139</v>
+      </c>
+      <c r="E96" s="24"/>
+      <c r="F96" s="24" t="s">
+        <v>21</v>
+      </c>
+      <c r="G96" s="24"/>
+      <c r="H96" s="24"/>
+      <c r="I96" s="24"/>
+      <c r="J96" s="24"/>
+      <c r="K96" s="24"/>
+    </row>
+    <row r="97" spans="1:11" s="2" customFormat="1" ht="15" x14ac:dyDescent="0.25">
+      <c r="A97" s="22">
+        <v>96</v>
+      </c>
+      <c r="B97" s="4" t="s">
+        <v>379</v>
+      </c>
+      <c r="C97" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="D97" s="4"/>
+      <c r="E97" s="4"/>
+      <c r="F97" s="4" t="s">
+        <v>348</v>
+      </c>
+      <c r="G97" s="4"/>
+      <c r="H97" s="4"/>
+      <c r="I97" s="4"/>
+      <c r="J97" s="4"/>
+      <c r="K97" s="4"/>
+    </row>
+    <row r="98" spans="1:11" ht="15" x14ac:dyDescent="0.25">
+      <c r="A98" s="22">
+        <v>97</v>
+      </c>
+      <c r="B98" s="6" t="s">
+        <v>140</v>
+      </c>
+      <c r="C98" s="6" t="s">
+        <v>100</v>
+      </c>
+      <c r="D98" s="6" t="s">
+        <v>141</v>
+      </c>
+      <c r="F98" s="6" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="99" spans="1:11" ht="15" x14ac:dyDescent="0.25">
+      <c r="A99" s="22">
+        <v>98</v>
+      </c>
+      <c r="B99" s="6" t="s">
+        <v>142</v>
+      </c>
+      <c r="C99" s="6" t="s">
+        <v>100</v>
+      </c>
+      <c r="D99" s="6" t="s">
+        <v>114</v>
+      </c>
+      <c r="F99" s="6" t="s">
+        <v>102</v>
+      </c>
+      <c r="G99" s="6" t="s">
+        <v>115</v>
+      </c>
+      <c r="H99" s="6" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="100" spans="1:11" ht="15" x14ac:dyDescent="0.25">
+      <c r="A100" s="22">
+        <v>99</v>
+      </c>
+      <c r="B100" s="6" t="s">
+        <v>143</v>
+      </c>
+      <c r="C100" s="6" t="s">
+        <v>100</v>
+      </c>
+      <c r="D100" s="6" t="s">
+        <v>144</v>
+      </c>
+      <c r="F100" s="6" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="101" spans="1:11" ht="15" x14ac:dyDescent="0.25">
+      <c r="A101" s="22">
+        <v>100</v>
+      </c>
+      <c r="B101" s="6" t="s">
+        <v>145</v>
+      </c>
+      <c r="C101" s="6" t="s">
+        <v>100</v>
+      </c>
+      <c r="D101" s="6" t="s">
+        <v>101</v>
+      </c>
+      <c r="F101" s="6" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="102" spans="1:11" ht="15" x14ac:dyDescent="0.25">
+      <c r="A102" s="22">
+        <v>101</v>
+      </c>
+      <c r="B102" s="6" t="s">
+        <v>146</v>
+      </c>
+      <c r="C102" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="D102" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="E102" s="6" t="s">
+        <v>147</v>
+      </c>
+      <c r="F102" s="6" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="103" spans="1:11" ht="15" x14ac:dyDescent="0.25">
+      <c r="A103" s="22">
+        <v>102</v>
+      </c>
+      <c r="B103" s="6" t="s">
+        <v>148</v>
+      </c>
+      <c r="C103" s="6" t="s">
+        <v>149</v>
+      </c>
+      <c r="D103" s="6" t="s">
+        <v>118</v>
+      </c>
+      <c r="F103" s="6" t="s">
+        <v>52</v>
+      </c>
+      <c r="K103" s="6" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="104" spans="1:11" ht="15" x14ac:dyDescent="0.25">
+      <c r="A104" s="22">
+        <v>103</v>
+      </c>
+      <c r="B104" s="6" t="s">
+        <v>151</v>
+      </c>
+      <c r="C104" s="6" t="s">
+        <v>149</v>
+      </c>
+      <c r="D104" s="6" t="s">
+        <v>82</v>
+      </c>
+      <c r="F104" s="6" t="s">
+        <v>52</v>
+      </c>
+      <c r="K104" s="6" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="105" spans="1:11" ht="15" x14ac:dyDescent="0.25">
+      <c r="A105" s="22">
+        <v>104</v>
+      </c>
+      <c r="B105" s="6" t="s">
+        <v>152</v>
+      </c>
+      <c r="C105" s="6" t="s">
+        <v>149</v>
+      </c>
+      <c r="D105" s="6" t="s">
+        <v>153</v>
+      </c>
+      <c r="F105" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="K105" s="6" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="106" spans="1:11" ht="15" x14ac:dyDescent="0.25">
+      <c r="A106" s="22">
+        <v>105</v>
+      </c>
+      <c r="B106" s="6" t="s">
+        <v>155</v>
+      </c>
+      <c r="C106" s="6" t="s">
+        <v>149</v>
+      </c>
+      <c r="D106" s="6" t="s">
+        <v>156</v>
+      </c>
+      <c r="F106" s="6" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="107" spans="1:11" ht="15" x14ac:dyDescent="0.25">
+      <c r="A107" s="22">
+        <v>106</v>
+      </c>
+      <c r="B107" s="6" t="s">
+        <v>157</v>
+      </c>
+      <c r="C107" s="6" t="s">
+        <v>158</v>
+      </c>
+      <c r="D107" s="6" t="s">
+        <v>159</v>
+      </c>
+      <c r="F107" s="6" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="108" spans="1:11" ht="15" x14ac:dyDescent="0.25">
+      <c r="A108" s="22">
+        <v>107</v>
+      </c>
+      <c r="B108" s="6" t="s">
+        <v>160</v>
+      </c>
+      <c r="C108" s="6" t="s">
+        <v>100</v>
+      </c>
+      <c r="D108" s="6" t="s">
+        <v>114</v>
+      </c>
+      <c r="F108" s="6" t="s">
+        <v>102</v>
+      </c>
+      <c r="G108" s="6" t="s">
+        <v>115</v>
+      </c>
+      <c r="H108" s="6" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="109" spans="1:11" ht="15" x14ac:dyDescent="0.25">
+      <c r="A109" s="22">
+        <v>108</v>
+      </c>
+      <c r="B109" s="6" t="s">
+        <v>161</v>
+      </c>
+      <c r="C109" s="6" t="s">
+        <v>100</v>
+      </c>
+      <c r="D109" s="6" t="s">
+        <v>101</v>
+      </c>
+      <c r="F109" s="6" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="110" spans="1:11" ht="15" x14ac:dyDescent="0.25">
+      <c r="A110" s="22">
+        <v>109</v>
+      </c>
+      <c r="B110" s="6" t="s">
+        <v>162</v>
+      </c>
+      <c r="C110" s="6" t="s">
+        <v>100</v>
+      </c>
+      <c r="D110" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="E110" s="6" t="s">
+        <v>163</v>
+      </c>
+      <c r="F110" s="6" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="111" spans="1:11" ht="15" x14ac:dyDescent="0.25">
+      <c r="A111" s="22">
+        <v>110</v>
+      </c>
+      <c r="B111" s="6" t="s">
+        <v>164</v>
+      </c>
+      <c r="C111" s="6" t="s">
+        <v>165</v>
+      </c>
+      <c r="D111" s="6" t="s">
+        <v>166</v>
+      </c>
+      <c r="F111" s="6" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="112" spans="1:11" ht="15" x14ac:dyDescent="0.25">
+      <c r="A112" s="22">
+        <v>111</v>
+      </c>
+      <c r="B112" s="6" t="s">
+        <v>167</v>
+      </c>
+      <c r="C112" s="6" t="s">
+        <v>165</v>
+      </c>
+      <c r="D112" s="6" t="s">
+        <v>168</v>
+      </c>
+      <c r="F112" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="K112" s="6" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="113" spans="1:11" ht="15" x14ac:dyDescent="0.25">
+      <c r="A113" s="22">
+        <v>112</v>
+      </c>
+      <c r="B113" s="6" t="s">
+        <v>169</v>
+      </c>
+      <c r="C113" s="6" t="s">
+        <v>165</v>
+      </c>
+      <c r="D113" s="6" t="s">
+        <v>170</v>
+      </c>
+      <c r="F113" s="6" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="114" spans="1:11" ht="15" x14ac:dyDescent="0.25">
+      <c r="A114" s="22">
+        <v>113</v>
+      </c>
+      <c r="B114" s="6" t="s">
+        <v>171</v>
+      </c>
+      <c r="C114" s="6" t="s">
+        <v>165</v>
+      </c>
+      <c r="D114" s="6" t="s">
+        <v>172</v>
+      </c>
+      <c r="F114" s="6" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="115" spans="1:11" ht="15" x14ac:dyDescent="0.25">
+      <c r="A115" s="22">
+        <v>114</v>
+      </c>
+      <c r="B115" s="6" t="s">
+        <v>173</v>
+      </c>
+      <c r="C115" s="6" t="s">
+        <v>165</v>
+      </c>
+      <c r="D115" s="6" t="s">
+        <v>174</v>
+      </c>
+      <c r="F115" s="6" t="s">
+        <v>52</v>
+      </c>
+      <c r="K115" s="6" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="116" spans="1:11" ht="15" x14ac:dyDescent="0.25">
+      <c r="A116" s="22">
+        <v>115</v>
+      </c>
+      <c r="B116" s="6" t="s">
+        <v>176</v>
+      </c>
+      <c r="C116" s="6" t="s">
+        <v>165</v>
+      </c>
+      <c r="D116" s="6" t="s">
+        <v>177</v>
+      </c>
+      <c r="F116" s="6" t="s">
+        <v>52</v>
+      </c>
+      <c r="K116" s="6" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="117" spans="1:11" ht="15" x14ac:dyDescent="0.25">
+      <c r="A117" s="22">
+        <v>116</v>
+      </c>
+      <c r="B117" s="6" t="s">
+        <v>179</v>
+      </c>
+      <c r="C117" s="6" t="s">
+        <v>165</v>
+      </c>
+      <c r="D117" s="6" t="s">
+        <v>180</v>
+      </c>
+      <c r="F117" s="6" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="118" spans="1:11" ht="15" x14ac:dyDescent="0.25">
+      <c r="A118" s="22">
+        <v>117</v>
+      </c>
+      <c r="B118" s="6" t="s">
+        <v>181</v>
+      </c>
+      <c r="C118" s="6" t="s">
+        <v>100</v>
+      </c>
+      <c r="D118" s="6" t="s">
+        <v>141</v>
+      </c>
+      <c r="F118" s="6" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="119" spans="1:11" ht="15" x14ac:dyDescent="0.25">
+      <c r="A119" s="22">
+        <v>118</v>
+      </c>
+      <c r="B119" s="6" t="s">
+        <v>182</v>
+      </c>
+      <c r="C119" s="6" t="s">
+        <v>100</v>
+      </c>
+      <c r="D119" s="6" t="s">
+        <v>183</v>
+      </c>
+      <c r="F119" s="6" t="s">
+        <v>102</v>
+      </c>
+      <c r="G119" s="6" t="s">
+        <v>115</v>
+      </c>
+      <c r="H119" s="6" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="120" spans="1:11" ht="15" x14ac:dyDescent="0.25">
+      <c r="A120" s="22">
+        <v>119</v>
+      </c>
+      <c r="B120" s="6" t="s">
+        <v>184</v>
+      </c>
+      <c r="C120" s="6" t="s">
+        <v>100</v>
+      </c>
+      <c r="D120" s="6" t="s">
+        <v>144</v>
+      </c>
+      <c r="F120" s="6" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="121" spans="1:11" ht="15" x14ac:dyDescent="0.25">
+      <c r="A121" s="22">
+        <v>120</v>
+      </c>
+      <c r="B121" s="6" t="s">
+        <v>185</v>
+      </c>
+      <c r="C121" s="6" t="s">
+        <v>100</v>
+      </c>
+      <c r="D121" s="6" t="s">
+        <v>101</v>
+      </c>
+      <c r="F121" s="6" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="122" spans="1:11" ht="15" x14ac:dyDescent="0.25">
+      <c r="A122" s="22">
+        <v>121</v>
+      </c>
+      <c r="B122" s="6" t="s">
+        <v>186</v>
+      </c>
+      <c r="C122" s="6" t="s">
+        <v>100</v>
+      </c>
+      <c r="D122" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="E122" s="6" t="s">
+        <v>187</v>
+      </c>
+      <c r="F122" s="6" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="123" spans="1:11" ht="15" x14ac:dyDescent="0.25">
+      <c r="A123" s="22">
+        <v>122</v>
+      </c>
+      <c r="B123" s="6" t="s">
+        <v>188</v>
+      </c>
+      <c r="C123" s="6" t="s">
+        <v>189</v>
+      </c>
+      <c r="D123" s="6" t="s">
+        <v>190</v>
+      </c>
+      <c r="F123" s="6" t="s">
+        <v>52</v>
+      </c>
+      <c r="K123" s="6" t="s">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="124" spans="1:11" ht="15" x14ac:dyDescent="0.25">
+      <c r="A124" s="22">
+        <v>123</v>
+      </c>
+      <c r="B124" s="6" t="s">
+        <v>192</v>
+      </c>
+      <c r="C124" s="6" t="s">
+        <v>189</v>
+      </c>
+      <c r="D124" s="6" t="s">
+        <v>193</v>
+      </c>
+      <c r="F124" s="6" t="s">
+        <v>52</v>
+      </c>
+      <c r="K124" s="6" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="125" spans="1:11" ht="15" x14ac:dyDescent="0.25">
+      <c r="A125" s="22">
+        <v>124</v>
+      </c>
+      <c r="B125" s="6" t="s">
+        <v>195</v>
+      </c>
+      <c r="C125" s="6" t="s">
+        <v>189</v>
+      </c>
+      <c r="D125" s="6" t="s">
+        <v>196</v>
+      </c>
+      <c r="F125" s="6" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="126" spans="1:11" ht="15" x14ac:dyDescent="0.25">
+      <c r="A126" s="22">
+        <v>125</v>
+      </c>
+      <c r="B126" s="6" t="s">
+        <v>197</v>
+      </c>
+      <c r="C126" s="6" t="s">
+        <v>189</v>
+      </c>
+      <c r="D126" s="6" t="s">
+        <v>198</v>
+      </c>
+      <c r="F126" s="6" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="127" spans="1:11" ht="15" x14ac:dyDescent="0.25">
+      <c r="A127" s="22">
+        <v>126</v>
+      </c>
+      <c r="B127" s="6" t="s">
+        <v>199</v>
+      </c>
+      <c r="C127" s="6" t="s">
+        <v>189</v>
+      </c>
+      <c r="D127" s="6" t="s">
+        <v>200</v>
+      </c>
+      <c r="F127" s="6" t="s">
+        <v>52</v>
+      </c>
+      <c r="J127" s="6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="128" spans="1:11" ht="15" x14ac:dyDescent="0.25">
+      <c r="A128" s="22">
+        <v>127</v>
+      </c>
+      <c r="B128" s="6" t="s">
+        <v>201</v>
+      </c>
+      <c r="C128" s="6" t="s">
+        <v>189</v>
+      </c>
+      <c r="D128" s="6" t="s">
+        <v>202</v>
+      </c>
+      <c r="F128" s="6" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="129" spans="1:11" ht="15" x14ac:dyDescent="0.25">
+      <c r="A129" s="22">
+        <v>128</v>
+      </c>
+      <c r="B129" s="6" t="s">
+        <v>203</v>
+      </c>
+      <c r="C129" s="6" t="s">
+        <v>189</v>
+      </c>
+      <c r="D129" s="6" t="s">
+        <v>204</v>
+      </c>
+      <c r="F129" s="6" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="130" spans="1:11" ht="15" x14ac:dyDescent="0.25">
+      <c r="A130" s="22">
+        <v>129</v>
+      </c>
+      <c r="B130" s="6" t="s">
+        <v>205</v>
+      </c>
+      <c r="C130" s="6" t="s">
+        <v>189</v>
+      </c>
+      <c r="D130" s="6" t="s">
+        <v>206</v>
+      </c>
+      <c r="F130" s="6" t="s">
+        <v>52</v>
+      </c>
+      <c r="K130" s="6" t="s">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="131" spans="1:11" ht="15" x14ac:dyDescent="0.25">
+      <c r="A131" s="22">
+        <v>130</v>
+      </c>
+      <c r="B131" s="6" t="s">
+        <v>208</v>
+      </c>
+      <c r="C131" s="6" t="s">
+        <v>189</v>
+      </c>
+      <c r="D131" s="6" t="s">
+        <v>139</v>
+      </c>
+      <c r="F131" s="6" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="132" spans="1:11" ht="15" x14ac:dyDescent="0.25">
+      <c r="A132" s="22">
+        <v>131</v>
+      </c>
+      <c r="B132" s="6" t="s">
+        <v>209</v>
+      </c>
+      <c r="C132" s="6" t="s">
+        <v>100</v>
+      </c>
+      <c r="D132" s="6" t="s">
+        <v>210</v>
+      </c>
+      <c r="F132" s="6" t="s">
+        <v>102</v>
+      </c>
+      <c r="G132" s="6" t="s">
+        <v>115</v>
+      </c>
+      <c r="H132" s="6" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="133" spans="1:11" ht="15" x14ac:dyDescent="0.25">
+      <c r="A133" s="22">
+        <v>132</v>
+      </c>
+      <c r="B133" s="6" t="s">
+        <v>211</v>
+      </c>
+      <c r="C133" s="6" t="s">
+        <v>100</v>
+      </c>
+      <c r="D133" s="6" t="s">
+        <v>101</v>
+      </c>
+      <c r="F133" s="6" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="134" spans="1:11" ht="15" x14ac:dyDescent="0.25">
+      <c r="A134" s="22">
+        <v>133</v>
+      </c>
+      <c r="B134" s="6" t="s">
+        <v>212</v>
+      </c>
+      <c r="C134" s="6" t="s">
+        <v>100</v>
+      </c>
+      <c r="D134" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="E134" s="6" t="s">
+        <v>213</v>
+      </c>
+      <c r="F134" s="6" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="135" spans="1:11" ht="15" x14ac:dyDescent="0.25">
+      <c r="A135" s="22">
         <v>134</v>
       </c>
-      <c r="D88" t="s">
+      <c r="B135" s="6" t="s">
+        <v>214</v>
+      </c>
+      <c r="C135" s="6" t="s">
+        <v>189</v>
+      </c>
+      <c r="D135" s="6" t="s">
+        <v>196</v>
+      </c>
+      <c r="F135" s="6" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="136" spans="1:11" ht="15" x14ac:dyDescent="0.25">
+      <c r="A136" s="22">
+        <v>135</v>
+      </c>
+      <c r="B136" s="6" t="s">
+        <v>215</v>
+      </c>
+      <c r="C136" s="6" t="s">
+        <v>189</v>
+      </c>
+      <c r="D136" s="6" t="s">
+        <v>216</v>
+      </c>
+      <c r="F136" s="6" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="137" spans="1:11" ht="15" x14ac:dyDescent="0.25">
+      <c r="A137" s="22">
+        <v>136</v>
+      </c>
+      <c r="B137" s="6" t="s">
+        <v>217</v>
+      </c>
+      <c r="C137" s="6" t="s">
+        <v>189</v>
+      </c>
+      <c r="D137" s="6" t="s">
+        <v>200</v>
+      </c>
+      <c r="F137" s="6" t="s">
+        <v>52</v>
+      </c>
+      <c r="J137" s="6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="138" spans="1:11" ht="15" x14ac:dyDescent="0.25">
+      <c r="A138" s="22">
+        <v>137</v>
+      </c>
+      <c r="B138" s="6" t="s">
+        <v>218</v>
+      </c>
+      <c r="C138" s="6" t="s">
+        <v>189</v>
+      </c>
+      <c r="D138" s="6" t="s">
+        <v>202</v>
+      </c>
+      <c r="F138" s="6" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="139" spans="1:11" ht="15" x14ac:dyDescent="0.25">
+      <c r="A139" s="22">
+        <v>138</v>
+      </c>
+      <c r="B139" s="6" t="s">
+        <v>219</v>
+      </c>
+      <c r="C139" s="6" t="s">
+        <v>189</v>
+      </c>
+      <c r="D139" s="6" t="s">
         <v>139</v>
       </c>
-      <c r="F88" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="89" spans="1:11" ht="15" x14ac:dyDescent="0.25">
-      <c r="A89" s="4">
-        <v>88</v>
-      </c>
-      <c r="B89" t="s">
+      <c r="F139" s="6" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="140" spans="1:11" ht="15" x14ac:dyDescent="0.25">
+      <c r="A140" s="22">
+        <v>139</v>
+      </c>
+      <c r="B140" s="6" t="s">
+        <v>220</v>
+      </c>
+      <c r="C140" s="6" t="s">
+        <v>100</v>
+      </c>
+      <c r="D140" s="6" t="s">
+        <v>221</v>
+      </c>
+      <c r="F140" s="6" t="s">
+        <v>102</v>
+      </c>
+      <c r="G140" s="6" t="s">
+        <v>115</v>
+      </c>
+      <c r="H140" s="6" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="141" spans="1:11" ht="15" x14ac:dyDescent="0.25">
+      <c r="A141" s="22">
         <v>140</v>
       </c>
-      <c r="C89" t="s">
-        <v>131</v>
-      </c>
-      <c r="D89" t="s">
+      <c r="B141" s="6" t="s">
+        <v>222</v>
+      </c>
+      <c r="C141" s="6" t="s">
+        <v>100</v>
+      </c>
+      <c r="D141" s="6" t="s">
+        <v>101</v>
+      </c>
+      <c r="F141" s="6" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="142" spans="1:11" ht="15" x14ac:dyDescent="0.25">
+      <c r="A142" s="22">
         <v>141</v>
       </c>
-      <c r="F89" t="s">
+      <c r="B142" s="6" t="s">
+        <v>223</v>
+      </c>
+      <c r="C142" s="6" t="s">
+        <v>100</v>
+      </c>
+      <c r="D142" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="E142" s="6" t="s">
+        <v>224</v>
+      </c>
+      <c r="F142" s="6" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="143" spans="1:11" ht="15" x14ac:dyDescent="0.25">
+      <c r="A143" s="22">
+        <v>142</v>
+      </c>
+      <c r="B143" s="6" t="s">
+        <v>225</v>
+      </c>
+      <c r="C143" s="6" t="s">
+        <v>226</v>
+      </c>
+      <c r="D143" s="6" t="s">
+        <v>227</v>
+      </c>
+      <c r="F143" s="6" t="s">
         <v>52</v>
       </c>
-      <c r="K89" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="90" spans="1:11" ht="15" x14ac:dyDescent="0.25">
-      <c r="A90" s="4">
-        <v>89</v>
-      </c>
-      <c r="B90" t="s">
-        <v>142</v>
-      </c>
-      <c r="C90" t="s">
-        <v>131</v>
-      </c>
-      <c r="D90" t="s">
+      <c r="K143" s="6" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="144" spans="1:11" ht="15" x14ac:dyDescent="0.25">
+      <c r="A144" s="22">
         <v>143</v>
       </c>
-      <c r="F90" t="s">
+      <c r="B144" s="6" t="s">
+        <v>229</v>
+      </c>
+      <c r="C144" s="6" t="s">
+        <v>226</v>
+      </c>
+      <c r="D144" s="6" t="s">
+        <v>230</v>
+      </c>
+      <c r="F144" s="6" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="145" spans="1:11" ht="15" x14ac:dyDescent="0.25">
+      <c r="A145" s="22">
+        <v>144</v>
+      </c>
+      <c r="B145" s="6" t="s">
+        <v>231</v>
+      </c>
+      <c r="C145" s="6" t="s">
+        <v>100</v>
+      </c>
+      <c r="D145" s="6" t="s">
+        <v>232</v>
+      </c>
+      <c r="F145" s="6" t="s">
+        <v>102</v>
+      </c>
+      <c r="G145" s="6" t="s">
+        <v>115</v>
+      </c>
+      <c r="H145" s="6" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="146" spans="1:11" ht="15" x14ac:dyDescent="0.25">
+      <c r="A146" s="22">
+        <v>145</v>
+      </c>
+      <c r="B146" s="6" t="s">
+        <v>233</v>
+      </c>
+      <c r="C146" s="6" t="s">
+        <v>100</v>
+      </c>
+      <c r="D146" s="6" t="s">
+        <v>101</v>
+      </c>
+      <c r="F146" s="6" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="147" spans="1:11" ht="15" x14ac:dyDescent="0.25">
+      <c r="A147" s="22">
+        <v>146</v>
+      </c>
+      <c r="B147" s="6" t="s">
+        <v>234</v>
+      </c>
+      <c r="C147" s="6" t="s">
+        <v>100</v>
+      </c>
+      <c r="D147" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="E147" s="6" t="s">
+        <v>235</v>
+      </c>
+      <c r="F147" s="6" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="148" spans="1:11" ht="15" x14ac:dyDescent="0.25">
+      <c r="A148" s="22">
+        <v>147</v>
+      </c>
+      <c r="B148" s="6" t="s">
+        <v>236</v>
+      </c>
+      <c r="C148" s="6" t="s">
+        <v>226</v>
+      </c>
+      <c r="D148" s="6" t="s">
+        <v>237</v>
+      </c>
+      <c r="F148" s="6" t="s">
         <v>52</v>
       </c>
-      <c r="J90" t="s">
-        <v>144</v>
-      </c>
-    </row>
-    <row r="91" spans="1:11" ht="15" x14ac:dyDescent="0.25">
-      <c r="A91" s="4">
-        <v>90</v>
-      </c>
-      <c r="B91" t="s">
-        <v>145</v>
-      </c>
-      <c r="C91" t="s">
-        <v>131</v>
-      </c>
-      <c r="D91" t="s">
+      <c r="K148" s="6" t="s">
+        <v>238</v>
+      </c>
+    </row>
+    <row r="149" spans="1:11" ht="15" x14ac:dyDescent="0.25">
+      <c r="A149" s="22">
+        <v>148</v>
+      </c>
+      <c r="B149" s="6" t="s">
+        <v>239</v>
+      </c>
+      <c r="C149" s="6" t="s">
+        <v>226</v>
+      </c>
+      <c r="D149" s="6" t="s">
+        <v>240</v>
+      </c>
+      <c r="F149" s="6" t="s">
+        <v>52</v>
+      </c>
+      <c r="K149" s="6" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="150" spans="1:11" ht="15" x14ac:dyDescent="0.25">
+      <c r="A150" s="22">
+        <v>149</v>
+      </c>
+      <c r="B150" s="6" t="s">
+        <v>242</v>
+      </c>
+      <c r="C150" s="6" t="s">
+        <v>226</v>
+      </c>
+      <c r="D150" s="6" t="s">
+        <v>243</v>
+      </c>
+      <c r="F150" s="6" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="151" spans="1:11" ht="15" x14ac:dyDescent="0.25">
+      <c r="A151" s="22">
+        <v>150</v>
+      </c>
+      <c r="B151" s="6" t="s">
+        <v>244</v>
+      </c>
+      <c r="C151" s="6" t="s">
         <v>100</v>
       </c>
-      <c r="F91" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="92" spans="1:11" ht="15" x14ac:dyDescent="0.25">
-      <c r="A92" s="4">
-        <v>91</v>
-      </c>
-      <c r="B92" t="s">
-        <v>146</v>
-      </c>
-      <c r="C92" t="s">
-        <v>147</v>
-      </c>
-      <c r="D92" t="s">
-        <v>148</v>
-      </c>
-      <c r="F92" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="93" spans="1:11" ht="15" x14ac:dyDescent="0.25">
-      <c r="A93" s="4">
-        <v>92</v>
-      </c>
-      <c r="B93" t="s">
-        <v>149</v>
-      </c>
-      <c r="C93" t="s">
-        <v>147</v>
-      </c>
-      <c r="D93" t="s">
-        <v>150</v>
-      </c>
-      <c r="F93" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="94" spans="1:11" ht="15" x14ac:dyDescent="0.25">
-      <c r="A94" s="4">
-        <v>93</v>
-      </c>
-      <c r="B94" t="s">
+      <c r="D151" s="6" t="s">
+        <v>141</v>
+      </c>
+      <c r="F151" s="6" t="s">
+        <v>102</v>
+      </c>
+      <c r="G151" s="6" t="s">
+        <v>103</v>
+      </c>
+      <c r="H151" s="6" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="152" spans="1:11" ht="15" x14ac:dyDescent="0.25">
+      <c r="A152" s="22">
         <v>151</v>
       </c>
-      <c r="C94" t="s">
-        <v>101</v>
-      </c>
-      <c r="D94" t="s">
+      <c r="B152" s="6" t="s">
+        <v>245</v>
+      </c>
+      <c r="C152" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="D152" s="6" t="s">
+        <v>246</v>
+      </c>
+      <c r="F152" s="6" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="153" spans="1:11" ht="15" x14ac:dyDescent="0.25">
+      <c r="A153" s="22">
         <v>152</v>
       </c>
-      <c r="F94" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="95" spans="1:11" ht="15" x14ac:dyDescent="0.25">
-      <c r="A95" s="4">
-        <v>94</v>
-      </c>
-      <c r="B95" t="s">
-        <v>153</v>
-      </c>
-      <c r="C95" t="s">
-        <v>101</v>
-      </c>
-      <c r="D95" t="s">
-        <v>116</v>
-      </c>
-      <c r="F95" t="s">
-        <v>103</v>
-      </c>
-      <c r="G95" t="s">
-        <v>117</v>
-      </c>
-      <c r="H95" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="96" spans="1:11" ht="15" x14ac:dyDescent="0.25">
-      <c r="A96" s="4">
-        <v>95</v>
-      </c>
-      <c r="B96" t="s">
-        <v>154</v>
-      </c>
-      <c r="C96" t="s">
-        <v>101</v>
-      </c>
-      <c r="D96" t="s">
-        <v>155</v>
-      </c>
-      <c r="F96" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="97" spans="1:11" ht="15" x14ac:dyDescent="0.25">
-      <c r="A97" s="4">
-        <v>96</v>
-      </c>
-      <c r="B97" t="s">
-        <v>156</v>
-      </c>
-      <c r="C97" t="s">
-        <v>101</v>
-      </c>
-      <c r="D97" t="s">
-        <v>102</v>
-      </c>
-      <c r="F97" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="98" spans="1:11" ht="15" x14ac:dyDescent="0.25">
-      <c r="A98" s="4">
-        <v>97</v>
-      </c>
-      <c r="B98" t="s">
-        <v>157</v>
-      </c>
-      <c r="C98" t="s">
+      <c r="B153" s="6" t="s">
+        <v>247</v>
+      </c>
+      <c r="C153" s="6" t="s">
         <v>19</v>
       </c>
-      <c r="D98" t="s">
-        <v>39</v>
-      </c>
-      <c r="E98" t="s">
-        <v>158</v>
-      </c>
-      <c r="F98" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="99" spans="1:11" ht="15" x14ac:dyDescent="0.25">
-      <c r="A99" s="4">
-        <v>98</v>
-      </c>
-      <c r="B99" t="s">
-        <v>159</v>
-      </c>
-      <c r="C99" t="s">
-        <v>160</v>
-      </c>
-      <c r="D99" t="s">
-        <v>122</v>
-      </c>
-      <c r="F99" t="s">
-        <v>52</v>
-      </c>
-      <c r="K99" t="s">
-        <v>161</v>
-      </c>
-    </row>
-    <row r="100" spans="1:11" ht="15" x14ac:dyDescent="0.25">
-      <c r="A100" s="4">
-        <v>99</v>
-      </c>
-      <c r="B100" t="s">
-        <v>162</v>
-      </c>
-      <c r="C100" t="s">
-        <v>160</v>
-      </c>
-      <c r="D100" t="s">
-        <v>83</v>
-      </c>
-      <c r="F100" t="s">
-        <v>52</v>
-      </c>
-      <c r="K100" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="101" spans="1:11" ht="15" x14ac:dyDescent="0.25">
-      <c r="A101" s="4">
-        <v>100</v>
-      </c>
-      <c r="B101" t="s">
-        <v>163</v>
-      </c>
-      <c r="C101" t="s">
-        <v>160</v>
-      </c>
-      <c r="D101" t="s">
-        <v>164</v>
-      </c>
-      <c r="F101" t="s">
-        <v>14</v>
-      </c>
-      <c r="K101" t="s">
-        <v>165</v>
-      </c>
-    </row>
-    <row r="102" spans="1:11" ht="15" x14ac:dyDescent="0.25">
-      <c r="A102" s="4">
-        <v>101</v>
-      </c>
-      <c r="B102" t="s">
-        <v>166</v>
-      </c>
-      <c r="C102" t="s">
-        <v>160</v>
-      </c>
-      <c r="D102" t="s">
-        <v>167</v>
-      </c>
-      <c r="F102" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="103" spans="1:11" ht="15" x14ac:dyDescent="0.25">
-      <c r="A103" s="4">
-        <v>102</v>
-      </c>
-      <c r="B103" t="s">
-        <v>168</v>
-      </c>
-      <c r="C103" t="s">
-        <v>169</v>
-      </c>
-      <c r="D103" t="s">
-        <v>170</v>
-      </c>
-      <c r="F103" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="104" spans="1:11" ht="15" x14ac:dyDescent="0.25">
-      <c r="A104" s="4">
-        <v>103</v>
-      </c>
-      <c r="B104" t="s">
-        <v>171</v>
-      </c>
-      <c r="C104" t="s">
-        <v>101</v>
-      </c>
-      <c r="D104" t="s">
-        <v>116</v>
-      </c>
-      <c r="F104" t="s">
-        <v>103</v>
-      </c>
-      <c r="G104" t="s">
-        <v>117</v>
-      </c>
-      <c r="H104" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="105" spans="1:11" ht="15" x14ac:dyDescent="0.25">
-      <c r="A105" s="4">
-        <v>104</v>
-      </c>
-      <c r="B105" t="s">
-        <v>172</v>
-      </c>
-      <c r="C105" t="s">
-        <v>101</v>
-      </c>
-      <c r="D105" t="s">
-        <v>102</v>
-      </c>
-      <c r="F105" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="106" spans="1:11" ht="15" x14ac:dyDescent="0.25">
-      <c r="A106" s="4">
-        <v>105</v>
-      </c>
-      <c r="B106" t="s">
-        <v>173</v>
-      </c>
-      <c r="C106" t="s">
-        <v>101</v>
-      </c>
-      <c r="D106" t="s">
-        <v>39</v>
-      </c>
-      <c r="E106" t="s">
-        <v>174</v>
-      </c>
-      <c r="F106" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="107" spans="1:11" ht="15" x14ac:dyDescent="0.25">
-      <c r="A107" s="4">
-        <v>106</v>
-      </c>
-      <c r="B107" t="s">
-        <v>175</v>
-      </c>
-      <c r="C107" t="s">
-        <v>176</v>
-      </c>
-      <c r="D107" t="s">
-        <v>177</v>
-      </c>
-      <c r="F107" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="108" spans="1:11" ht="15" x14ac:dyDescent="0.25">
-      <c r="A108" s="4">
-        <v>107</v>
-      </c>
-      <c r="B108" t="s">
-        <v>178</v>
-      </c>
-      <c r="C108" t="s">
-        <v>176</v>
-      </c>
-      <c r="D108" t="s">
-        <v>179</v>
-      </c>
-      <c r="F108" t="s">
-        <v>14</v>
-      </c>
-      <c r="K108" t="s">
-        <v>136</v>
-      </c>
-    </row>
-    <row r="109" spans="1:11" ht="15" x14ac:dyDescent="0.25">
-      <c r="A109" s="4">
-        <v>108</v>
-      </c>
-      <c r="B109" t="s">
-        <v>180</v>
-      </c>
-      <c r="C109" t="s">
-        <v>176</v>
-      </c>
-      <c r="D109" t="s">
-        <v>181</v>
-      </c>
-      <c r="F109" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="110" spans="1:11" ht="15" x14ac:dyDescent="0.25">
-      <c r="A110" s="4">
-        <v>109</v>
-      </c>
-      <c r="B110" t="s">
-        <v>182</v>
-      </c>
-      <c r="C110" t="s">
-        <v>176</v>
-      </c>
-      <c r="D110" t="s">
-        <v>183</v>
-      </c>
-      <c r="F110" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="111" spans="1:11" ht="15" x14ac:dyDescent="0.25">
-      <c r="A111" s="4">
-        <v>110</v>
-      </c>
-      <c r="B111" t="s">
-        <v>184</v>
-      </c>
-      <c r="C111" t="s">
-        <v>176</v>
-      </c>
-      <c r="D111" t="s">
-        <v>185</v>
-      </c>
-      <c r="F111" t="s">
-        <v>52</v>
-      </c>
-      <c r="K111" t="s">
-        <v>186</v>
-      </c>
-    </row>
-    <row r="112" spans="1:11" ht="15" x14ac:dyDescent="0.25">
-      <c r="A112" s="4">
-        <v>111</v>
-      </c>
-      <c r="B112" t="s">
-        <v>187</v>
-      </c>
-      <c r="C112" t="s">
-        <v>176</v>
-      </c>
-      <c r="D112" t="s">
-        <v>188</v>
-      </c>
-      <c r="F112" t="s">
-        <v>52</v>
-      </c>
-      <c r="K112" t="s">
-        <v>189</v>
-      </c>
-    </row>
-    <row r="113" spans="1:11" ht="15" x14ac:dyDescent="0.25">
-      <c r="A113" s="4">
-        <v>112</v>
-      </c>
-      <c r="B113" t="s">
-        <v>190</v>
-      </c>
-      <c r="C113" t="s">
-        <v>176</v>
-      </c>
-      <c r="D113" t="s">
-        <v>191</v>
-      </c>
-      <c r="F113" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="114" spans="1:11" ht="15" x14ac:dyDescent="0.25">
-      <c r="A114" s="4">
-        <v>113</v>
-      </c>
-      <c r="B114" t="s">
-        <v>192</v>
-      </c>
-      <c r="C114" t="s">
-        <v>101</v>
-      </c>
-      <c r="D114" t="s">
-        <v>152</v>
-      </c>
-      <c r="F114" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="115" spans="1:11" ht="15" x14ac:dyDescent="0.25">
-      <c r="A115" s="4">
-        <v>114</v>
-      </c>
-      <c r="B115" t="s">
-        <v>193</v>
-      </c>
-      <c r="C115" t="s">
-        <v>101</v>
-      </c>
-      <c r="D115" t="s">
-        <v>194</v>
-      </c>
-      <c r="F115" t="s">
-        <v>103</v>
-      </c>
-      <c r="G115" t="s">
-        <v>117</v>
-      </c>
-      <c r="H115" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="116" spans="1:11" ht="15" x14ac:dyDescent="0.25">
-      <c r="A116" s="4">
-        <v>115</v>
-      </c>
-      <c r="B116" t="s">
-        <v>195</v>
-      </c>
-      <c r="C116" t="s">
-        <v>101</v>
-      </c>
-      <c r="D116" t="s">
-        <v>155</v>
-      </c>
-      <c r="F116" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="117" spans="1:11" ht="15" x14ac:dyDescent="0.25">
-      <c r="A117" s="4">
-        <v>116</v>
-      </c>
-      <c r="B117" t="s">
-        <v>196</v>
-      </c>
-      <c r="C117" t="s">
-        <v>101</v>
-      </c>
-      <c r="D117" t="s">
-        <v>102</v>
-      </c>
-      <c r="F117" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="118" spans="1:11" ht="15" x14ac:dyDescent="0.25">
-      <c r="A118" s="4">
-        <v>117</v>
-      </c>
-      <c r="B118" t="s">
-        <v>197</v>
-      </c>
-      <c r="C118" t="s">
-        <v>101</v>
-      </c>
-      <c r="D118" t="s">
-        <v>39</v>
-      </c>
-      <c r="E118" t="s">
-        <v>198</v>
-      </c>
-      <c r="F118" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="119" spans="1:11" ht="15" x14ac:dyDescent="0.25">
-      <c r="A119" s="4">
-        <v>118</v>
-      </c>
-      <c r="B119" t="s">
-        <v>199</v>
-      </c>
-      <c r="C119" t="s">
-        <v>200</v>
-      </c>
-      <c r="D119" t="s">
-        <v>201</v>
-      </c>
-      <c r="F119" t="s">
-        <v>52</v>
-      </c>
-      <c r="K119" t="s">
-        <v>202</v>
-      </c>
-    </row>
-    <row r="120" spans="1:11" ht="15" x14ac:dyDescent="0.25">
-      <c r="A120" s="4">
-        <v>119</v>
-      </c>
-      <c r="B120" t="s">
-        <v>203</v>
-      </c>
-      <c r="C120" t="s">
-        <v>200</v>
-      </c>
-      <c r="D120" t="s">
-        <v>204</v>
-      </c>
-      <c r="F120" t="s">
-        <v>52</v>
-      </c>
-      <c r="K120" t="s">
-        <v>205</v>
-      </c>
-    </row>
-    <row r="121" spans="1:11" ht="15" x14ac:dyDescent="0.25">
-      <c r="A121" s="4">
-        <v>120</v>
-      </c>
-      <c r="B121" t="s">
-        <v>206</v>
-      </c>
-      <c r="C121" t="s">
-        <v>200</v>
-      </c>
-      <c r="D121" t="s">
-        <v>207</v>
-      </c>
-      <c r="F121" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="122" spans="1:11" ht="15" x14ac:dyDescent="0.25">
-      <c r="A122" s="4">
-        <v>121</v>
-      </c>
-      <c r="B122" t="s">
-        <v>208</v>
-      </c>
-      <c r="C122" t="s">
-        <v>200</v>
-      </c>
-      <c r="D122" t="s">
-        <v>209</v>
-      </c>
-      <c r="F122" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="123" spans="1:11" ht="15" x14ac:dyDescent="0.25">
-      <c r="A123" s="4">
-        <v>122</v>
-      </c>
-      <c r="B123" t="s">
-        <v>210</v>
-      </c>
-      <c r="C123" t="s">
-        <v>200</v>
-      </c>
-      <c r="D123" t="s">
-        <v>211</v>
-      </c>
-      <c r="F123" t="s">
-        <v>52</v>
-      </c>
-      <c r="J123">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="124" spans="1:11" ht="15" x14ac:dyDescent="0.25">
-      <c r="A124" s="4">
-        <v>123</v>
-      </c>
-      <c r="B124" t="s">
-        <v>212</v>
-      </c>
-      <c r="C124" t="s">
-        <v>200</v>
-      </c>
-      <c r="D124" t="s">
-        <v>213</v>
-      </c>
-      <c r="F124" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="125" spans="1:11" ht="15" x14ac:dyDescent="0.25">
-      <c r="A125" s="4">
-        <v>124</v>
-      </c>
-      <c r="B125" t="s">
-        <v>214</v>
-      </c>
-      <c r="C125" t="s">
-        <v>200</v>
-      </c>
-      <c r="D125" t="s">
-        <v>215</v>
-      </c>
-      <c r="F125" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="126" spans="1:11" ht="15" x14ac:dyDescent="0.25">
-      <c r="A126" s="4">
-        <v>125</v>
-      </c>
-      <c r="B126" t="s">
-        <v>216</v>
-      </c>
-      <c r="C126" t="s">
-        <v>200</v>
-      </c>
-      <c r="D126" t="s">
-        <v>217</v>
-      </c>
-      <c r="F126" t="s">
-        <v>52</v>
-      </c>
-      <c r="K126" t="s">
-        <v>218</v>
-      </c>
-    </row>
-    <row r="127" spans="1:11" ht="15" x14ac:dyDescent="0.25">
-      <c r="A127" s="4">
-        <v>126</v>
-      </c>
-      <c r="B127" t="s">
-        <v>219</v>
-      </c>
-      <c r="C127" t="s">
-        <v>200</v>
-      </c>
-      <c r="D127" t="s">
-        <v>150</v>
-      </c>
-      <c r="F127" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="128" spans="1:11" ht="15" x14ac:dyDescent="0.25">
-      <c r="A128" s="4">
-        <v>127</v>
-      </c>
-      <c r="B128" t="s">
-        <v>220</v>
-      </c>
-      <c r="C128" t="s">
-        <v>101</v>
-      </c>
-      <c r="D128" t="s">
-        <v>221</v>
-      </c>
-      <c r="F128" t="s">
-        <v>103</v>
-      </c>
-      <c r="G128" t="s">
-        <v>117</v>
-      </c>
-      <c r="H128" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="129" spans="1:11" ht="15" x14ac:dyDescent="0.25">
-      <c r="A129" s="4">
-        <v>128</v>
-      </c>
-      <c r="B129" t="s">
-        <v>222</v>
-      </c>
-      <c r="C129" t="s">
-        <v>101</v>
-      </c>
-      <c r="D129" t="s">
-        <v>102</v>
-      </c>
-      <c r="F129" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="130" spans="1:11" ht="15" x14ac:dyDescent="0.25">
-      <c r="A130" s="4">
-        <v>129</v>
-      </c>
-      <c r="B130" t="s">
-        <v>223</v>
-      </c>
-      <c r="C130" t="s">
-        <v>101</v>
-      </c>
-      <c r="D130" t="s">
-        <v>39</v>
-      </c>
-      <c r="E130" t="s">
-        <v>224</v>
-      </c>
-      <c r="F130" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="131" spans="1:11" ht="15" x14ac:dyDescent="0.25">
-      <c r="A131" s="4">
-        <v>130</v>
-      </c>
-      <c r="B131" t="s">
-        <v>225</v>
-      </c>
-      <c r="C131" t="s">
-        <v>200</v>
-      </c>
-      <c r="D131" t="s">
-        <v>207</v>
-      </c>
-      <c r="F131" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="132" spans="1:11" ht="15" x14ac:dyDescent="0.25">
-      <c r="A132" s="4">
-        <v>131</v>
-      </c>
-      <c r="B132" t="s">
-        <v>226</v>
-      </c>
-      <c r="C132" t="s">
-        <v>200</v>
-      </c>
-      <c r="D132" t="s">
-        <v>227</v>
-      </c>
-      <c r="F132" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="133" spans="1:11" ht="15" x14ac:dyDescent="0.25">
-      <c r="A133" s="4">
-        <v>132</v>
-      </c>
-      <c r="B133" t="s">
-        <v>228</v>
-      </c>
-      <c r="C133" t="s">
-        <v>200</v>
-      </c>
-      <c r="D133" t="s">
-        <v>211</v>
-      </c>
-      <c r="F133" t="s">
-        <v>52</v>
-      </c>
-      <c r="J133">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="134" spans="1:11" ht="15" x14ac:dyDescent="0.25">
-      <c r="A134" s="4">
-        <v>133</v>
-      </c>
-      <c r="B134" t="s">
-        <v>229</v>
-      </c>
-      <c r="C134" t="s">
-        <v>200</v>
-      </c>
-      <c r="D134" t="s">
-        <v>213</v>
-      </c>
-      <c r="F134" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="135" spans="1:11" ht="15" x14ac:dyDescent="0.25">
-      <c r="A135" s="4">
-        <v>134</v>
-      </c>
-      <c r="B135" t="s">
-        <v>230</v>
-      </c>
-      <c r="C135" t="s">
-        <v>200</v>
-      </c>
-      <c r="D135" t="s">
-        <v>150</v>
-      </c>
-      <c r="F135" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="136" spans="1:11" ht="15" x14ac:dyDescent="0.25">
-      <c r="A136" s="4">
-        <v>135</v>
-      </c>
-      <c r="B136" t="s">
-        <v>231</v>
-      </c>
-      <c r="C136" t="s">
-        <v>101</v>
-      </c>
-      <c r="D136" t="s">
-        <v>232</v>
-      </c>
-      <c r="F136" t="s">
-        <v>103</v>
-      </c>
-      <c r="G136" t="s">
-        <v>117</v>
-      </c>
-      <c r="H136" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="137" spans="1:11" ht="15" x14ac:dyDescent="0.25">
-      <c r="A137" s="4">
-        <v>136</v>
-      </c>
-      <c r="B137" t="s">
-        <v>233</v>
-      </c>
-      <c r="C137" t="s">
-        <v>101</v>
-      </c>
-      <c r="D137" t="s">
-        <v>102</v>
-      </c>
-      <c r="F137" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="138" spans="1:11" ht="15" x14ac:dyDescent="0.25">
-      <c r="A138" s="4">
-        <v>137</v>
-      </c>
-      <c r="B138" t="s">
-        <v>234</v>
-      </c>
-      <c r="C138" t="s">
-        <v>101</v>
-      </c>
-      <c r="D138" t="s">
-        <v>39</v>
-      </c>
-      <c r="E138" t="s">
-        <v>235</v>
-      </c>
-      <c r="F138" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="139" spans="1:11" ht="15" x14ac:dyDescent="0.25">
-      <c r="A139" s="4">
-        <v>138</v>
-      </c>
-      <c r="B139" t="s">
-        <v>236</v>
-      </c>
-      <c r="C139" t="s">
-        <v>237</v>
-      </c>
-      <c r="D139" t="s">
-        <v>238</v>
-      </c>
-      <c r="F139" t="s">
-        <v>52</v>
-      </c>
-      <c r="K139" t="s">
-        <v>239</v>
-      </c>
-    </row>
-    <row r="140" spans="1:11" ht="15" x14ac:dyDescent="0.25">
-      <c r="A140" s="4">
-        <v>139</v>
-      </c>
-      <c r="B140" t="s">
-        <v>240</v>
-      </c>
-      <c r="C140" t="s">
-        <v>237</v>
-      </c>
-      <c r="D140" t="s">
-        <v>241</v>
-      </c>
-      <c r="F140" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="141" spans="1:11" ht="15" x14ac:dyDescent="0.25">
-      <c r="A141" s="4">
-        <v>140</v>
-      </c>
-      <c r="B141" t="s">
-        <v>242</v>
-      </c>
-      <c r="C141" t="s">
-        <v>101</v>
-      </c>
-      <c r="D141" t="s">
-        <v>243</v>
-      </c>
-      <c r="F141" t="s">
-        <v>103</v>
-      </c>
-      <c r="G141" t="s">
-        <v>117</v>
-      </c>
-      <c r="H141" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="142" spans="1:11" ht="15" x14ac:dyDescent="0.25">
-      <c r="A142" s="4">
-        <v>141</v>
-      </c>
-      <c r="B142" t="s">
-        <v>244</v>
-      </c>
-      <c r="C142" t="s">
-        <v>101</v>
-      </c>
-      <c r="D142" t="s">
-        <v>102</v>
-      </c>
-      <c r="F142" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="143" spans="1:11" ht="15" x14ac:dyDescent="0.25">
-      <c r="A143" s="4">
-        <v>142</v>
-      </c>
-      <c r="B143" t="s">
-        <v>245</v>
-      </c>
-      <c r="C143" t="s">
-        <v>101</v>
-      </c>
-      <c r="D143" t="s">
-        <v>39</v>
-      </c>
-      <c r="E143" t="s">
-        <v>246</v>
-      </c>
-      <c r="F143" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="144" spans="1:11" ht="15" x14ac:dyDescent="0.25">
-      <c r="A144" s="4">
-        <v>143</v>
-      </c>
-      <c r="B144" t="s">
-        <v>247</v>
-      </c>
-      <c r="C144" t="s">
-        <v>237</v>
-      </c>
-      <c r="D144" t="s">
+      <c r="D153" s="6" t="s">
         <v>248</v>
       </c>
-      <c r="F144" t="s">
-        <v>52</v>
-      </c>
-      <c r="K144" t="s">
-        <v>249</v>
-      </c>
-    </row>
-    <row r="145" spans="1:11" ht="15" x14ac:dyDescent="0.25">
-      <c r="A145" s="4">
-        <v>144</v>
-      </c>
-      <c r="B145" t="s">
-        <v>250</v>
-      </c>
-      <c r="C145" t="s">
-        <v>237</v>
-      </c>
-      <c r="D145" t="s">
-        <v>251</v>
-      </c>
-      <c r="F145" t="s">
-        <v>52</v>
-      </c>
-      <c r="K145" t="s">
-        <v>252</v>
-      </c>
-    </row>
-    <row r="146" spans="1:11" ht="15" x14ac:dyDescent="0.25">
-      <c r="A146" s="4">
-        <v>145</v>
-      </c>
-      <c r="B146" t="s">
-        <v>253</v>
-      </c>
-      <c r="C146" t="s">
-        <v>237</v>
-      </c>
-      <c r="D146" t="s">
-        <v>254</v>
-      </c>
-      <c r="F146" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="147" spans="1:11" ht="15" x14ac:dyDescent="0.25">
-      <c r="A147" s="4">
-        <v>146</v>
-      </c>
-      <c r="B147" t="s">
-        <v>255</v>
-      </c>
-      <c r="C147" t="s">
-        <v>101</v>
-      </c>
-      <c r="D147" t="s">
-        <v>152</v>
-      </c>
-      <c r="F147" t="s">
-        <v>103</v>
-      </c>
-      <c r="G147" t="s">
-        <v>104</v>
-      </c>
-      <c r="H147" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="148" spans="1:11" ht="15" x14ac:dyDescent="0.25">
-      <c r="A148" s="4">
-        <v>147</v>
-      </c>
-      <c r="B148" t="s">
-        <v>256</v>
-      </c>
-      <c r="C148" t="s">
-        <v>19</v>
-      </c>
-      <c r="D148" t="s">
-        <v>257</v>
-      </c>
-      <c r="F148" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="149" spans="1:11" ht="15" x14ac:dyDescent="0.25">
-      <c r="A149" s="4">
-        <v>148</v>
-      </c>
-      <c r="B149" t="s">
-        <v>258</v>
-      </c>
-      <c r="C149" t="s">
-        <v>19</v>
-      </c>
-      <c r="D149" t="s">
-        <v>259</v>
-      </c>
-      <c r="F149" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="150" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A150" s="24"/>
-    </row>
-    <row r="151" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B151" s="16" t="s">
-        <v>28</v>
-      </c>
-      <c r="C151" s="17" t="s">
-        <v>380</v>
-      </c>
-      <c r="D151" s="18" t="s">
-        <v>377</v>
-      </c>
-    </row>
-    <row r="152" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B152" s="16" t="s">
-        <v>28</v>
-      </c>
-      <c r="C152" s="17" t="s">
-        <v>381</v>
-      </c>
-      <c r="D152" s="19" t="s">
-        <v>378</v>
-      </c>
-    </row>
-    <row r="153" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B153" s="16" t="s">
-        <v>28</v>
-      </c>
-      <c r="C153" s="19" t="s">
-        <v>382</v>
-      </c>
-      <c r="D153" s="19" t="s">
-        <v>383</v>
-      </c>
-    </row>
-    <row r="154" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B154" s="15"/>
-      <c r="C154" s="14"/>
+      <c r="F153" s="6" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="155" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B155" s="11"/>
+      <c r="C155" s="23"/>
+      <c r="D155" s="11"/>
+    </row>
+    <row r="156" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B156" s="11"/>
+      <c r="C156" s="23"/>
+      <c r="D156" s="24"/>
+    </row>
+    <row r="157" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B157" s="11"/>
+      <c r="C157" s="24"/>
+      <c r="D157" s="24"/>
+    </row>
+    <row r="158" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B158" s="10"/>
+      <c r="C158" s="25"/>
+    </row>
+    <row r="159" spans="1:11" s="15" customFormat="1" ht="15" x14ac:dyDescent="0.25">
+      <c r="A159" s="28"/>
+      <c r="B159" s="14"/>
+      <c r="C159" s="14"/>
+      <c r="D159" s="26"/>
+      <c r="E159" s="14"/>
+      <c r="F159" s="14"/>
+      <c r="G159" s="14"/>
+      <c r="H159" s="14"/>
+      <c r="I159" s="14"/>
+      <c r="J159" s="14"/>
+      <c r="K159" s="14"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:K1" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
-  <dataValidations count="5">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F26 F24 F57 F34 F37 F60 F62 F65 F68 F74 F71" xr:uid="{A78A6BD1-DBA3-4AF4-AD65-FEE2CB211C08}">
+  <dataValidations count="6">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F27 F25 F58 F35 F38 F61 F63 F66 F69 F74 F72" xr:uid="{FAE72E79-4708-456B-865C-32AD917BB854}">
       <formula1>IF(ISBLANK(#REF!), INDIRECT("keywordnotreqpage"), IF(ISBLANK(#REF!), INDIRECT("keywordnotreqelement"), INDIRECT(LEFT(#REF!,3)&amp;"")))</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G27 G64" xr:uid="{4B2CB004-F64C-451A-BDCF-479F4421E3D6}">
-      <formula1>IF(COUNTIF(keywordreqproperty,F27)&gt;0,property,(IF(COUNTIF(keywordreqstyle,F27)&gt;0,style,"")))</formula1>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G28 G65 G79" xr:uid="{501A2280-FDEB-4069-A72F-46159BB76ACF}">
+      <formula1>IF(COUNTIF(keywordreqproperty,F28)&gt;0,property,(IF(COUNTIF(keywordreqstyle,F28)&gt;0,style,"")))</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H27 H64" xr:uid="{B3DDA236-59FA-4F7B-8AE3-1ED013943F31}">
-      <formula1>IF(COUNTIF(keywordreqtablecondition,F27)&gt;0,tablecondition,(IF(COUNTIF(keywordreqcondition,F27)&gt;0,condition,"")))</formula1>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H28 H65 H79" xr:uid="{CADCA75F-1479-459A-B80B-29FA53AEC59B}">
+      <formula1>IF(COUNTIF(keywordreqtablecondition,F28)&gt;0,tablecondition,(IF(COUNTIF(keywordreqcondition,F28)&gt;0,condition,"")))</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F38:F41 F58:F59 F48:F56 F27:F28 F63" xr:uid="{9CC71B15-59EE-40C2-B495-02AD90749506}">
-      <formula1>IF(ISBLANK(C27), INDIRECT("keywordnotreqpage"), IF(ISBLANK(D27), INDIRECT("keywordnotreqelement"), INDIRECT(LEFT(D27,3)&amp;"")))</formula1>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F39:F42 F59:F60 F49:F57 F28:F29 F64 F85" xr:uid="{0DA4D09D-16B4-48B8-B8D4-15EBC60A6B6B}">
+      <formula1>IF(ISBLANK(C28), INDIRECT("keywordnotreqpage"), IF(ISBLANK(D28), INDIRECT("keywordnotreqelement"), INDIRECT(LEFT(D28,3)&amp;"")))</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F64" xr:uid="{E77BC152-4FAA-49BA-8B7A-39E3C988DAD7}">
-      <formula1>IF(ISBLANK(C122), INDIRECT("keywordnotreqpage"), IF(ISBLANK(D122), INDIRECT("keywordnotreqelement"), INDIRECT(LEFT(D122,3)&amp;"")))</formula1>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F84 F91 F86" xr:uid="{30338E8C-796D-453C-BA92-1F47EEE044E4}">
+      <formula1>IF(ISBLANK(C144), INDIRECT("keywordnotreqpage"), IF(ISBLANK(D144), INDIRECT("keywordnotreqelement"), INDIRECT(LEFT(D144,3)&amp;"")))</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F65 F81:F82 F79 F97" xr:uid="{0D8DEEA9-564B-41DD-B319-C984911E59D4}">
+      <formula1>IF(ISBLANK(C126), INDIRECT("keywordnotreqpage"), IF(ISBLANK(D126), INDIRECT("keywordnotreqelement"), INDIRECT(LEFT(D126,3)&amp;"")))</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -5079,84 +5318,84 @@
   <sheetData>
     <row r="1" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>328</v>
+        <v>317</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="L1" s="1" t="s">
-        <v>123</v>
+        <v>119</v>
       </c>
       <c r="M1" s="1" t="s">
-        <v>126</v>
+        <v>122</v>
       </c>
       <c r="N1" s="1" t="s">
-        <v>136</v>
+        <v>128</v>
       </c>
       <c r="O1" s="1" t="s">
-        <v>161</v>
+        <v>150</v>
       </c>
       <c r="P1" s="1" t="s">
-        <v>165</v>
+        <v>154</v>
       </c>
       <c r="Q1" s="1" t="s">
-        <v>186</v>
+        <v>175</v>
       </c>
       <c r="R1" s="1" t="s">
-        <v>189</v>
+        <v>178</v>
       </c>
       <c r="S1" s="1" t="s">
-        <v>202</v>
+        <v>191</v>
       </c>
       <c r="T1" s="1" t="s">
-        <v>205</v>
+        <v>194</v>
       </c>
       <c r="U1" s="1" t="s">
-        <v>218</v>
+        <v>207</v>
       </c>
       <c r="V1" s="1" t="s">
-        <v>239</v>
+        <v>228</v>
       </c>
       <c r="W1" s="1" t="s">
-        <v>249</v>
+        <v>238</v>
       </c>
       <c r="X1" s="1" t="s">
-        <v>252</v>
+        <v>241</v>
       </c>
     </row>
     <row r="2" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>260</v>
+        <v>249</v>
       </c>
       <c r="B2" t="s">
-        <v>261</v>
+        <v>250</v>
       </c>
       <c r="C2" t="s">
         <v>32</v>
@@ -5165,64 +5404,64 @@
         <v>3</v>
       </c>
       <c r="E2" t="s">
-        <v>329</v>
+        <v>318</v>
       </c>
       <c r="F2" t="s">
-        <v>335</v>
+        <v>324</v>
       </c>
       <c r="G2" t="s">
-        <v>336</v>
+        <v>325</v>
       </c>
       <c r="H2" t="s">
         <v>26</v>
       </c>
       <c r="I2" t="s">
-        <v>337</v>
+        <v>326</v>
       </c>
       <c r="J2" t="s">
-        <v>262</v>
+        <v>251</v>
       </c>
       <c r="K2" t="s">
-        <v>263</v>
+        <v>252</v>
       </c>
       <c r="L2" t="s">
-        <v>264</v>
+        <v>253</v>
       </c>
       <c r="M2" t="s">
-        <v>265</v>
+        <v>254</v>
       </c>
       <c r="N2">
         <v>996289289500</v>
       </c>
       <c r="O2" t="s">
-        <v>264</v>
+        <v>253</v>
       </c>
       <c r="P2">
         <v>5</v>
       </c>
       <c r="Q2" t="s">
-        <v>266</v>
+        <v>255</v>
       </c>
       <c r="R2" t="s">
-        <v>267</v>
+        <v>256</v>
       </c>
       <c r="S2" t="s">
-        <v>268</v>
+        <v>257</v>
       </c>
       <c r="T2" t="s">
-        <v>269</v>
+        <v>258</v>
       </c>
       <c r="U2" t="s">
-        <v>270</v>
+        <v>259</v>
       </c>
       <c r="V2" t="s">
-        <v>271</v>
+        <v>260</v>
       </c>
       <c r="W2" t="s">
-        <v>272</v>
+        <v>261</v>
       </c>
       <c r="X2" t="s">
-        <v>273</v>
+        <v>262</v>
       </c>
     </row>
   </sheetData>
@@ -5241,71 +5480,71 @@
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>274</v>
+        <v>263</v>
       </c>
       <c r="B1" s="3" t="s">
-        <v>275</v>
+        <v>264</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>276</v>
+        <v>265</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>277</v>
+        <v>266</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>278</v>
+        <v>267</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>279</v>
+        <v>268</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>280</v>
+        <v>269</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>281</v>
+        <v>270</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>282</v>
+        <v>271</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>283</v>
+        <v>272</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>284</v>
+        <v>273</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>285</v>
+        <v>274</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>286</v>
+        <v>275</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>287</v>
+        <v>276</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>288</v>
+        <v>277</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>289</v>
+        <v>278</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>290</v>
+        <v>279</v>
       </c>
       <c r="B9" s="3">
         <v>108</v>
@@ -5313,7 +5552,7 @@
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>291</v>
+        <v>280</v>
       </c>
       <c r="B10" s="3">
         <v>20</v>
@@ -5321,7 +5560,7 @@
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>292</v>
+        <v>281</v>
       </c>
       <c r="B11" s="3">
         <v>77</v>
@@ -5329,15 +5568,15 @@
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>293</v>
+        <v>282</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>294</v>
+        <v>283</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>295</v>
+        <v>284</v>
       </c>
       <c r="B13" s="3">
         <v>46147</v>
@@ -5345,7 +5584,7 @@
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>296</v>
+        <v>285</v>
       </c>
       <c r="B14" s="3">
         <v>46147</v>
@@ -5353,31 +5592,31 @@
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>297</v>
+        <v>286</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>298</v>
+        <v>287</v>
       </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>299</v>
+        <v>288</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>300</v>
+        <v>289</v>
       </c>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>301</v>
+        <v>290</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>302</v>
+        <v>291</v>
       </c>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>303</v>
+        <v>292</v>
       </c>
       <c r="B18" s="3">
         <v>9</v>
@@ -5385,18 +5624,18 @@
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>304</v>
+        <v>293</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>305</v>
+        <v>294</v>
       </c>
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>306</v>
+        <v>295</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>307</v>
+        <v>296</v>
       </c>
     </row>
   </sheetData>
@@ -5416,13 +5655,13 @@
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>308</v>
+        <v>297</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>282</v>
+        <v>271</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>309</v>
+        <v>298</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
@@ -5430,10 +5669,10 @@
         <v>50</v>
       </c>
       <c r="B2" t="s">
-        <v>310</v>
+        <v>299</v>
       </c>
       <c r="C2" t="s">
-        <v>311</v>
+        <v>300</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
@@ -5441,10 +5680,10 @@
         <v>996289289500</v>
       </c>
       <c r="B3" t="s">
-        <v>312</v>
+        <v>301</v>
       </c>
       <c r="C3" t="s">
-        <v>313</v>
+        <v>302</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
@@ -5452,10 +5691,10 @@
         <v>17</v>
       </c>
       <c r="B4" t="s">
-        <v>314</v>
+        <v>303</v>
       </c>
       <c r="C4" t="s">
-        <v>313</v>
+        <v>302</v>
       </c>
     </row>
   </sheetData>

--- a/lorenzo-playwright-kdf/excelFramework/testcases/IP/LSTP_IP_WF001.xlsx
+++ b/lorenzo-playwright-kdf/excelFramework/testcases/IP/LSTP_IP_WF001.xlsx
@@ -3,9 +3,9 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
   <workbookPr filterPrivacy="1" updateLinks="always" defaultThemeVersion="202300"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A3844345-1C02-4532-8273-E682E8B5920E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5B9103E2-F1A6-4B4E-BDD8-089568FCCFB3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-16320" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="TestExecution" sheetId="1" r:id="rId1"/>
@@ -2080,7 +2080,7 @@
         <v>18</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="D4" s="3" t="s">
         <v>20</v>

--- a/lorenzo-playwright-kdf/excelFramework/testcases/IP/LSTP_IP_WF001.xlsx
+++ b/lorenzo-playwright-kdf/excelFramework/testcases/IP/LSTP_IP_WF001.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
   <workbookPr filterPrivacy="1" updateLinks="always" defaultThemeVersion="202300"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5B9103E2-F1A6-4B4E-BDD8-089568FCCFB3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BA2C5F5A-B42B-4516-8BF5-F8F488271507}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-16320" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -46,7 +46,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1070" uniqueCount="418">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1070" uniqueCount="417">
   <si>
     <t>StepNo</t>
   </si>
@@ -1248,15 +1248,6 @@
     <t>TRANSFER_LOCATION</t>
   </si>
   <si>
-    <t>//Click on Allocate NHS YES</t>
-  </si>
-  <si>
-    <t>//Click on No in Has this person had NHS No pop up</t>
-  </si>
-  <si>
-    <t>//Select finish button PDSSynchronisation</t>
-  </si>
-  <si>
     <t>selectIPHistoryByHeader</t>
   </si>
   <si>
@@ -1299,7 +1290,13 @@
     <t>//validation patient hisotry values</t>
   </si>
   <si>
-    <t>//Select the Appointment details validation from inpatient history</t>
+    <t>Click on Allocate NHS YES</t>
+  </si>
+  <si>
+    <t>Click on No in Has this person had NHS No pop up</t>
+  </si>
+  <si>
+    <t>Select finish button PDSSynchronisation</t>
   </si>
 </sst>
 </file>
@@ -2094,7 +2091,7 @@
         <v>4</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>408</v>
+        <v>405</v>
       </c>
       <c r="C5" s="3" t="s">
         <v>19</v>
@@ -2128,7 +2125,7 @@
         <v>6</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>408</v>
+        <v>405</v>
       </c>
       <c r="C7" s="3" t="s">
         <v>19</v>
@@ -2574,7 +2571,7 @@
         <v>29</v>
       </c>
       <c r="B30" s="3" t="s">
-        <v>400</v>
+        <v>414</v>
       </c>
       <c r="C30" s="3" t="s">
         <v>69</v>
@@ -2591,7 +2588,7 @@
         <v>30</v>
       </c>
       <c r="B31" s="3" t="s">
-        <v>401</v>
+        <v>415</v>
       </c>
       <c r="C31" s="3" t="s">
         <v>69</v>
@@ -3344,7 +3341,7 @@
         <v>72</v>
       </c>
       <c r="B73" s="3" t="s">
-        <v>408</v>
+        <v>405</v>
       </c>
       <c r="C73" s="3" t="s">
         <v>312</v>
@@ -3362,22 +3359,22 @@
         <v>73</v>
       </c>
       <c r="B74" s="3" t="s">
-        <v>407</v>
+        <v>404</v>
       </c>
       <c r="C74" s="3" t="s">
         <v>312</v>
       </c>
       <c r="D74" s="23" t="s">
-        <v>404</v>
+        <v>401</v>
       </c>
       <c r="E74" s="3"/>
       <c r="F74" s="22" t="s">
-        <v>403</v>
+        <v>400</v>
       </c>
       <c r="G74" s="3"/>
       <c r="H74" s="3"/>
       <c r="I74" s="22" t="s">
-        <v>406</v>
+        <v>403</v>
       </c>
       <c r="J74" s="3" t="s">
         <v>334</v>
@@ -3957,22 +3954,22 @@
         <v>107</v>
       </c>
       <c r="B108" s="3" t="s">
-        <v>411</v>
+        <v>408</v>
       </c>
       <c r="C108" s="3" t="s">
         <v>312</v>
       </c>
       <c r="D108" s="23" t="s">
-        <v>404</v>
+        <v>401</v>
       </c>
       <c r="E108" s="3"/>
       <c r="F108" s="22" t="s">
-        <v>403</v>
+        <v>400</v>
       </c>
       <c r="G108" s="3"/>
       <c r="H108" s="3"/>
       <c r="I108" s="22" t="s">
-        <v>406</v>
+        <v>403</v>
       </c>
       <c r="J108" s="3" t="s">
         <v>329</v>
@@ -4031,7 +4028,7 @@
         <v>111</v>
       </c>
       <c r="B112" s="3" t="s">
-        <v>402</v>
+        <v>416</v>
       </c>
       <c r="C112" s="3" t="s">
         <v>19</v>
@@ -4744,7 +4741,7 @@
         <v>152</v>
       </c>
       <c r="B153" s="3" t="s">
-        <v>408</v>
+        <v>405</v>
       </c>
       <c r="C153" s="3" t="s">
         <v>312</v>
@@ -4762,22 +4759,22 @@
         <v>153</v>
       </c>
       <c r="B154" s="3" t="s">
-        <v>411</v>
+        <v>408</v>
       </c>
       <c r="C154" s="3" t="s">
         <v>312</v>
       </c>
       <c r="D154" s="23" t="s">
-        <v>404</v>
+        <v>401</v>
       </c>
       <c r="E154" s="3"/>
       <c r="F154" s="22" t="s">
-        <v>403</v>
+        <v>400</v>
       </c>
       <c r="G154" s="3"/>
       <c r="H154" s="3"/>
       <c r="I154" s="22" t="s">
-        <v>406</v>
+        <v>403</v>
       </c>
       <c r="J154" s="3" t="s">
         <v>353</v>
@@ -4789,22 +4786,22 @@
         <v>154</v>
       </c>
       <c r="B155" s="3" t="s">
-        <v>417</v>
+        <v>408</v>
       </c>
       <c r="C155" s="3" t="s">
         <v>312</v>
       </c>
       <c r="D155" s="23" t="s">
-        <v>404</v>
+        <v>401</v>
       </c>
       <c r="E155" s="3"/>
       <c r="F155" s="22" t="s">
-        <v>403</v>
+        <v>400</v>
       </c>
       <c r="G155" s="3"/>
       <c r="H155" s="3"/>
       <c r="I155" s="22" t="s">
-        <v>415</v>
+        <v>412</v>
       </c>
       <c r="J155" s="3" t="s">
         <v>356</v>
@@ -4816,25 +4813,25 @@
         <v>155</v>
       </c>
       <c r="B156" s="3" t="s">
-        <v>417</v>
+        <v>408</v>
       </c>
       <c r="C156" s="3" t="s">
         <v>312</v>
       </c>
       <c r="D156" s="23" t="s">
-        <v>404</v>
+        <v>401</v>
       </c>
       <c r="E156" s="3"/>
       <c r="F156" s="22" t="s">
-        <v>403</v>
+        <v>400</v>
       </c>
       <c r="G156" s="3"/>
       <c r="H156" s="3"/>
       <c r="I156" s="22" t="s">
-        <v>409</v>
+        <v>406</v>
       </c>
       <c r="J156" s="3" t="s">
-        <v>414</v>
+        <v>411</v>
       </c>
       <c r="K156" s="24"/>
     </row>
@@ -4906,7 +4903,7 @@
         <v>159</v>
       </c>
       <c r="B160" s="15" t="s">
-        <v>405</v>
+        <v>402</v>
       </c>
       <c r="C160" s="15" t="s">
         <v>312</v>
@@ -4933,25 +4930,25 @@
         <v>160</v>
       </c>
       <c r="B161" s="22" t="s">
-        <v>416</v>
+        <v>413</v>
       </c>
       <c r="C161" s="22" t="s">
         <v>312</v>
       </c>
       <c r="D161" s="23" t="s">
-        <v>404</v>
+        <v>401</v>
       </c>
       <c r="E161" s="22"/>
       <c r="F161" s="22" t="s">
-        <v>403</v>
+        <v>400</v>
       </c>
       <c r="G161" s="22"/>
       <c r="H161" s="22"/>
       <c r="I161" s="22" t="s">
-        <v>413</v>
+        <v>410</v>
       </c>
       <c r="J161" s="22" t="s">
-        <v>410</v>
+        <v>407</v>
       </c>
       <c r="K161" s="22"/>
     </row>
@@ -5569,7 +5566,7 @@
         <v>196</v>
       </c>
       <c r="B197" s="3" t="s">
-        <v>408</v>
+        <v>405</v>
       </c>
       <c r="C197" s="3" t="s">
         <v>312</v>
@@ -5587,22 +5584,22 @@
         <v>197</v>
       </c>
       <c r="B198" s="3" t="s">
-        <v>411</v>
+        <v>408</v>
       </c>
       <c r="C198" s="3" t="s">
         <v>312</v>
       </c>
       <c r="D198" s="23" t="s">
-        <v>404</v>
+        <v>401</v>
       </c>
       <c r="E198" s="3"/>
       <c r="F198" s="22" t="s">
-        <v>403</v>
+        <v>400</v>
       </c>
       <c r="G198" s="3"/>
       <c r="H198" s="3"/>
       <c r="I198" s="22" t="s">
-        <v>406</v>
+        <v>403</v>
       </c>
       <c r="J198" s="3" t="s">
         <v>179</v>
@@ -5818,7 +5815,7 @@
         <v>210</v>
       </c>
       <c r="B211" s="3" t="s">
-        <v>408</v>
+        <v>405</v>
       </c>
       <c r="C211" s="3" t="s">
         <v>312</v>
@@ -5836,22 +5833,22 @@
         <v>211</v>
       </c>
       <c r="B212" s="3" t="s">
-        <v>412</v>
+        <v>409</v>
       </c>
       <c r="C212" s="3" t="s">
         <v>312</v>
       </c>
       <c r="D212" s="23" t="s">
-        <v>404</v>
+        <v>401</v>
       </c>
       <c r="E212" s="3"/>
       <c r="F212" s="22" t="s">
-        <v>403</v>
+        <v>400</v>
       </c>
       <c r="G212" s="3"/>
       <c r="H212" s="3"/>
       <c r="I212" s="22" t="s">
-        <v>406</v>
+        <v>403</v>
       </c>
       <c r="J212" s="3" t="s">
         <v>386</v>
@@ -6084,7 +6081,7 @@
         <v>225</v>
       </c>
       <c r="B226" s="3" t="s">
-        <v>408</v>
+        <v>405</v>
       </c>
       <c r="C226" s="3" t="s">
         <v>312</v>
@@ -6102,22 +6099,22 @@
         <v>226</v>
       </c>
       <c r="B227" s="3" t="s">
-        <v>412</v>
+        <v>409</v>
       </c>
       <c r="C227" s="3" t="s">
         <v>312</v>
       </c>
       <c r="D227" s="23" t="s">
-        <v>404</v>
+        <v>401</v>
       </c>
       <c r="E227" s="3"/>
       <c r="F227" s="22" t="s">
-        <v>403</v>
+        <v>400</v>
       </c>
       <c r="G227" s="3"/>
       <c r="H227" s="3"/>
       <c r="I227" s="22" t="s">
-        <v>406</v>
+        <v>403</v>
       </c>
       <c r="J227" s="3" t="s">
         <v>207</v>

--- a/lorenzo-playwright-kdf/excelFramework/testcases/IP/LSTP_IP_WF001.xlsx
+++ b/lorenzo-playwright-kdf/excelFramework/testcases/IP/LSTP_IP_WF001.xlsx
@@ -3,9 +3,9 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
   <workbookPr filterPrivacy="1" updateLinks="always" defaultThemeVersion="202300"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BA2C5F5A-B42B-4516-8BF5-F8F488271507}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{345E6371-891A-44EC-A2A1-BE2EEB881B8D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-16320" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="TestExecution" sheetId="1" r:id="rId1"/>

--- a/lorenzo-playwright-kdf/excelFramework/testcases/IP/LSTP_IP_WF001.xlsx
+++ b/lorenzo-playwright-kdf/excelFramework/testcases/IP/LSTP_IP_WF001.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
   <workbookPr filterPrivacy="1" updateLinks="always" defaultThemeVersion="202300"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{345E6371-891A-44EC-A2A1-BE2EEB881B8D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2C66AAB4-642C-404C-9F62-FD1325349C2C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -46,7 +46,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1070" uniqueCount="417">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1070" uniqueCount="418">
   <si>
     <t>StepNo</t>
   </si>
@@ -1297,6 +1297,9 @@
   </si>
   <si>
     <t>Select finish button PDSSynchronisation</t>
+  </si>
+  <si>
+    <t>launchRegistration</t>
   </si>
 </sst>
 </file>
@@ -2455,7 +2458,7 @@
         <v>61</v>
       </c>
       <c r="F23" s="3" t="s">
-        <v>21</v>
+        <v>417</v>
       </c>
     </row>
     <row r="24" spans="1:12" ht="15" x14ac:dyDescent="0.25">
@@ -2512,7 +2515,7 @@
         <v>286</v>
       </c>
       <c r="F26" s="3" t="s">
-        <v>21</v>
+        <v>417</v>
       </c>
     </row>
     <row r="27" spans="1:12" ht="15" x14ac:dyDescent="0.25">
